--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -692,12 +692,12 @@
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L2" s="16" t="inlineStr">
         <is>
-          <t>maa://39402, *maa://30515, *maa://34787</t>
+          <t>maa://39402, *maa://34787</t>
         </is>
       </c>
       <c r="M2" s="13" t="n"/>
@@ -1440,7 +1440,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.14 13:21:08</t>
+          <t>更新日期：2025.06.15 13:20:11</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="H27" s="16" t="inlineStr">
         <is>
-          <t>*maa://39601, maa://34494</t>
+          <t>maa://39601, maa://34494</t>
         </is>
       </c>
       <c r="I27" s="13" t="n"/>
@@ -6914,7 +6914,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.14 13:21:08</t>
+          <t>更新日期：2025.06.15 13:20:11</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1443,7 +1443,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.29 13:23:12</t>
+          <t>更新日期：2025.06.30 13:23:46</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -6917,7 +6917,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>更新日期：2025.06.29 13:23:12</t>
+          <t>更新日期：2025.06.30 13:23:46</t>
         </is>
       </c>
       <c r="E1" s="14" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D108" s="17" t="inlineStr">
         <is>
-          <t>maa://25018, maa://51881, maa://25776, maa://28361, maa://25772, maa://56588, maa://45194, maa://32653, maa://25161, maa://60902</t>
+          <t>maa://25018, maa://51881, maa://25776, maa://28361, maa://25772, maa://56588, maa://45194, maa://32653, maa://25161, **maa://60902</t>
         </is>
       </c>
     </row>
@@ -13239,7 +13239,7 @@
       </c>
       <c r="D272" s="17" t="inlineStr">
         <is>
-          <t>maa://51881, maa://51630, maa://56588, *maa://55171, maa://51893, maa://60902</t>
+          <t>maa://51881, maa://51630, maa://56588, *maa://55171, maa://51893, **maa://60902</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://59493, maa://59603, maa://60449</t>
+          <t>maa://59493, maa://60449, maa://59603</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1446,7 +1446,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.16 13:27:18</t>
+          <t>更新日期：2025.07.19 13:26:03</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="AF8" s="18" t="inlineStr">
         <is>
-          <t>*maa://24479, *maa://21990</t>
+          <t>*maa://24479, **maa://21990</t>
         </is>
       </c>
       <c r="AG8" s="12" t="n"/>
@@ -3666,12 +3666,12 @@
       </c>
       <c r="C25" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>maa://29753</t>
+          <t>maa://29753, maa://63016</t>
         </is>
       </c>
       <c r="E25" s="15" t="n"/>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AF39" s="18" t="inlineStr">
         <is>
-          <t>*maa://62953</t>
+          <t>maa://62953</t>
         </is>
       </c>
       <c r="AG39" s="12" t="n"/>
@@ -6971,7 +6971,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.16 13:27:18</t>
+          <t>更新日期：2025.07.19 13:26:03</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="D32" s="19" t="inlineStr">
         <is>
-          <t>maa://36644, maa://36866, maa://45572, maa://27794, maa://20960, maa://20843, **maa://24483, maa://62759, maa://20862, *maa://20893</t>
+          <t>maa://36644, maa://36866, maa://45572, maa://27794, maa://62759, maa://20960, maa://20843, **maa://24483, maa://20862, *maa://20893</t>
         </is>
       </c>
     </row>
@@ -10198,56 +10198,56 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>月禾</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>DM-3</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D132" s="19" t="inlineStr">
         <is>
-          <t>maa://20837, maa://37666</t>
+          <t>maa://39146</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>波登可</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t>maa://29023, maa://39515</t>
+          <t>maa://20856</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>月禾</t>
+          <t>苦艾</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
@@ -10257,19 +10257,19 @@
       </c>
       <c r="D134" s="19" t="inlineStr">
         <is>
-          <t>maa://39146</t>
+          <t>maa://20913</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>波登可</t>
+          <t>莱恩哈特</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -10279,19 +10279,19 @@
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t>maa://20856</t>
+          <t>maa://41856</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>苦艾</t>
+          <t>早露</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
@@ -10301,41 +10301,41 @@
       </c>
       <c r="D136" s="19" t="inlineStr">
         <is>
-          <t>maa://20913</t>
+          <t>maa://29025</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>莱恩哈特</t>
+          <t>卡达</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D137" s="19" t="inlineStr">
         <is>
-          <t>maa://41856</t>
+          <t>**maa://30679, maa://45258</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>早露</t>
+          <t>亚叶</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -10345,129 +10345,129 @@
       </c>
       <c r="D138" s="19" t="inlineStr">
         <is>
-          <t>maa://29025</t>
+          <t>maa://20981</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>卡达</t>
+          <t>断崖</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D139" s="19" t="inlineStr">
         <is>
-          <t>**maa://30679, maa://45258</t>
+          <t>maa://37689</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>亚叶</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>TW-7</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D140" s="19" t="inlineStr">
         <is>
-          <t>maa://20981</t>
+          <t>maa://28484, maa://31185, maa://30306</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>断崖</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D141" s="19" t="inlineStr">
         <is>
-          <t>maa://37689</t>
+          <t>maa://30670, maa://31470, *maa://45066</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>稀音</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>TW-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D142" s="19" t="inlineStr">
         <is>
-          <t>maa://28484, maa://31185, maa://30306</t>
+          <t>maa://20971</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>蜜蜡</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D143" s="19" t="inlineStr">
         <is>
-          <t>maa://30670, maa://31470, *maa://45066</t>
+          <t>maa://39147</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>稀音</t>
+          <t>贾维</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
@@ -10477,19 +10477,19 @@
       </c>
       <c r="D144" s="19" t="inlineStr">
         <is>
-          <t>maa://20971</t>
+          <t>maa://20898</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>蜜蜡</t>
+          <t>孑</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>S3-2</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
@@ -10499,129 +10499,129 @@
       </c>
       <c r="D145" s="19" t="inlineStr">
         <is>
-          <t>maa://39147</t>
+          <t>maa://29056</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>贾维</t>
+          <t>安哲拉</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D146" s="19" t="inlineStr">
         <is>
-          <t>maa://20898</t>
+          <t>maa://28828, maa://20846, *maa://47286</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>孑</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>S3-2</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D147" s="19" t="inlineStr">
         <is>
-          <t>maa://29056</t>
+          <t>maa://40957, maa://36641, maa://36865, maa://44635, maa://44660, maa://41128, maa://42918, maa://44119, maa://46108, maa://37300, maa://42917</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>安哲拉</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D148" s="19" t="inlineStr">
         <is>
-          <t>maa://28828, maa://20846, *maa://47286</t>
+          <t>maa://51549, maa://51923</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>酸糖</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D149" s="19" t="inlineStr">
         <is>
-          <t>maa://40957, maa://36641, maa://36865, maa://44635, maa://44660, maa://41128, maa://42918, maa://44119, maa://46108, maa://37300, maa://42917</t>
+          <t>maa://20961</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>特米米</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>RI-2</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D150" s="19" t="inlineStr">
         <is>
-          <t>maa://51549, maa://51923</t>
+          <t>maa://20963</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>酸糖</t>
+          <t>燧石</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>RI-9</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
@@ -10631,41 +10631,41 @@
       </c>
       <c r="D151" s="19" t="inlineStr">
         <is>
-          <t>maa://20961</t>
+          <t>maa://39148</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>特米米</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>RI-2</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D152" s="19" t="inlineStr">
         <is>
-          <t>maa://20963</t>
+          <t>maa://20946, maa://20833</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>燧石</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>RI-9</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
@@ -10675,41 +10675,41 @@
       </c>
       <c r="D153" s="19" t="inlineStr">
         <is>
-          <t>maa://39148</t>
+          <t>maa://20945</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>芳汀</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D154" s="19" t="inlineStr">
         <is>
-          <t>maa://20946, maa://20833</t>
+          <t>maa://37694</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>薄绿</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
@@ -10719,19 +10719,19 @@
       </c>
       <c r="D155" s="19" t="inlineStr">
         <is>
-          <t>maa://20945</t>
+          <t>*maa://39149</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>芳汀</t>
+          <t>四月</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
@@ -10741,41 +10741,41 @@
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>maa://37694</t>
+          <t>maa://20959</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>薄绿</t>
+          <t>史尔特尔</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D157" s="19" t="inlineStr">
         <is>
-          <t>*maa://39149</t>
+          <t>maa://44232, maa://45603</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>四月</t>
+          <t>泡泡</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
@@ -10785,41 +10785,41 @@
       </c>
       <c r="D158" s="19" t="inlineStr">
         <is>
-          <t>maa://20959</t>
+          <t>maa://20936</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>史尔特尔</t>
+          <t>鞭刃</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D159" s="19" t="inlineStr">
         <is>
-          <t>maa://44232, maa://45603</t>
+          <t>maa://20855</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>泡泡</t>
+          <t>奥斯塔</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -10829,41 +10829,41 @@
       </c>
       <c r="D160" s="19" t="inlineStr">
         <is>
-          <t>maa://20936</t>
+          <t>maa://40158</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>鞭刃</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>MN-4</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D161" s="19" t="inlineStr">
         <is>
-          <t>maa://20855</t>
+          <t>*maa://32845, maa://29054</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>奥斯塔</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -10873,63 +10873,63 @@
       </c>
       <c r="D162" s="19" t="inlineStr">
         <is>
-          <t>maa://40158</t>
+          <t>maa://20973</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>杰克</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>MN-4</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>*maa://32845, maa://29054</t>
+          <t>maa://39150</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>絮雨</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D164" s="19" t="inlineStr">
         <is>
-          <t>maa://20973</t>
+          <t>maa://20975, *maa://47950, maa://30806</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>杰克</t>
+          <t>迷迭香</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
@@ -10939,107 +10939,107 @@
       </c>
       <c r="D165" s="19" t="inlineStr">
         <is>
-          <t>maa://39150</t>
+          <t>maa://29059</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>絮雨</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D166" s="19" t="inlineStr">
         <is>
-          <t>maa://20975, *maa://47950, maa://30806</t>
+          <t>maa://45556</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>松果</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D167" s="19" t="inlineStr">
         <is>
-          <t>maa://29633, maa://29627, maa://29659, maa://49074, **maa://30679, maa://29861, maa://42343</t>
+          <t>maa://40159</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>罗宾</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>10-16</t>
+          <t>BI-EX-2</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D168" s="19" t="inlineStr">
         <is>
-          <t>maa://49867, maa://49655</t>
+          <t>maa://39152</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>迷迭香</t>
+          <t>卡夫卡</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D169" s="19" t="inlineStr">
         <is>
-          <t>maa://29059</t>
+          <t>*maa://20905, *maa://52268</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>LE-5</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
@@ -11049,41 +11049,41 @@
       </c>
       <c r="D170" s="19" t="inlineStr">
         <is>
-          <t>maa://45556</t>
+          <t>maa://59681</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>松果</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>MB-EX-3</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D171" s="19" t="inlineStr">
         <is>
-          <t>maa://40159</t>
+          <t>maa://32418, maa://51440</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>罗宾</t>
+          <t>豆苗</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>BI-EX-2</t>
+          <t>S3-7</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
@@ -11093,41 +11093,41 @@
       </c>
       <c r="D172" s="19" t="inlineStr">
         <is>
-          <t>maa://39152</t>
+          <t>maa://37690</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>卡夫卡</t>
+          <t>爱丽丝</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D173" s="19" t="inlineStr">
         <is>
-          <t>*maa://20905, *maa://52268</t>
+          <t>maa://20842</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>LE-5</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -11137,19 +11137,19 @@
       </c>
       <c r="D174" s="19" t="inlineStr">
         <is>
-          <t>maa://59681</t>
+          <t>maa://20912</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>MB-EX-3</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -11159,19 +11159,19 @@
       </c>
       <c r="D175" s="19" t="inlineStr">
         <is>
-          <t>maa://32418, maa://51440</t>
+          <t>maa://20911, maa://29012</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>豆苗</t>
+          <t>图耶</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>S3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
@@ -11181,19 +11181,19 @@
       </c>
       <c r="D176" s="19" t="inlineStr">
         <is>
-          <t>maa://37690</t>
+          <t>maa://20964</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>爱丽丝</t>
+          <t>炎狱炎熔</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>WR-4</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
@@ -11203,63 +11203,63 @@
       </c>
       <c r="D177" s="19" t="inlineStr">
         <is>
-          <t>maa://20842</t>
+          <t>maa://20983</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>乌有</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D178" s="19" t="inlineStr">
         <is>
-          <t>maa://20912</t>
+          <t>maa://31560, *maa://20968</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>WR-3</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D179" s="19" t="inlineStr">
         <is>
-          <t>maa://20911, maa://29012</t>
+          <t>maa://28104</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>图耶</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>WR-1</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
@@ -11269,19 +11269,19 @@
       </c>
       <c r="D180" s="19" t="inlineStr">
         <is>
-          <t>maa://20964</t>
+          <t>maa://20861</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>炎狱炎熔</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>WR-4</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
@@ -11291,19 +11291,19 @@
       </c>
       <c r="D181" s="19" t="inlineStr">
         <is>
-          <t>maa://20983</t>
+          <t>maa://20970</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>乌有</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
@@ -11313,19 +11313,19 @@
       </c>
       <c r="D182" s="19" t="inlineStr">
         <is>
-          <t>maa://31560, *maa://20968</t>
+          <t>maa://20969, maa://41303</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>WR-3</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
@@ -11335,19 +11335,19 @@
       </c>
       <c r="D183" s="19" t="inlineStr">
         <is>
-          <t>maa://28104</t>
+          <t>maa://20999</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>闪击</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>WR-1</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
@@ -11357,19 +11357,19 @@
       </c>
       <c r="D184" s="19" t="inlineStr">
         <is>
-          <t>maa://20861</t>
+          <t>maa://35198</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>霜华</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -11379,19 +11379,19 @@
       </c>
       <c r="D185" s="19" t="inlineStr">
         <is>
-          <t>maa://20970</t>
+          <t>maa://39153</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>SV-8</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
@@ -11401,41 +11401,41 @@
       </c>
       <c r="D186" s="19" t="inlineStr">
         <is>
-          <t>maa://20969, maa://41303</t>
+          <t>maa://34866, maa://34714</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D187" s="19" t="inlineStr">
         <is>
-          <t>maa://20999</t>
+          <t>maa://34883, maa://20895</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>闪击</t>
+          <t>暴雨</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
@@ -11445,19 +11445,19 @@
       </c>
       <c r="D188" s="19" t="inlineStr">
         <is>
-          <t>maa://35198</t>
+          <t>maa://20853</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>霜华</t>
+          <t>熔泉</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -11467,41 +11467,41 @@
       </c>
       <c r="D189" s="19" t="inlineStr">
         <is>
-          <t>maa://39153</t>
+          <t>maa://20942</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>SV-8</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D190" s="19" t="inlineStr">
         <is>
-          <t>maa://34866, maa://34714</t>
+          <t>maa://20992</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -11511,19 +11511,19 @@
       </c>
       <c r="D191" s="19" t="inlineStr">
         <is>
-          <t>maa://34883, maa://20895</t>
+          <t>*maa://28190, maa://20994</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>暴雨</t>
+          <t>赤冬</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
@@ -11533,85 +11533,85 @@
       </c>
       <c r="D192" s="19" t="inlineStr">
         <is>
-          <t>maa://20853</t>
+          <t>maa://20860</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>熔泉</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>SV-EX-5</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D193" s="19" t="inlineStr">
         <is>
-          <t>maa://20942</t>
+          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://20872, maa://51066, maa://63024</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>SN-EX-3</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D194" s="19" t="inlineStr">
         <is>
-          <t>maa://20992</t>
+          <t>maa://39156, *maa://39550, *maa://53417</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>浊心斯卡蒂</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D195" s="19" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20994</t>
+          <t>maa://42223, maa://49077, maa://42292, maa://42402</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>赤冬</t>
+          <t>深靛</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -11621,129 +11621,129 @@
       </c>
       <c r="D196" s="19" t="inlineStr">
         <is>
-          <t>maa://20860</t>
+          <t>maa://39154</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>贝娜</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-5</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D197" s="19" t="inlineStr">
         <is>
-          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://20872, maa://51066</t>
+          <t>maa://20854</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>绮良</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>SN-EX-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D198" s="19" t="inlineStr">
         <is>
-          <t>maa://39156, *maa://39550, *maa://53417</t>
+          <t>maa://20937</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D199" s="19" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>maa://22468</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D200" s="19" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>maa://30673, maa://30672</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>浊心斯卡蒂</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D201" s="19" t="inlineStr">
         <is>
-          <t>maa://42223, maa://49077, maa://42292, maa://42402</t>
+          <t>maa://20934, maa://20827, maa://20828</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>深靛</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
@@ -11753,19 +11753,19 @@
       </c>
       <c r="D202" s="19" t="inlineStr">
         <is>
-          <t>maa://39154</t>
+          <t>maa://20935</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>贝娜</t>
+          <t>龙舌兰</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -11775,107 +11775,107 @@
       </c>
       <c r="D203" s="19" t="inlineStr">
         <is>
-          <t>maa://20854</t>
+          <t>maa://53354</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>绮良</t>
+          <t>羽毛笔</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D204" s="19" t="inlineStr">
         <is>
-          <t>maa://20937</t>
+          <t>maa://28133, maa://25369</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D205" s="19" t="inlineStr">
         <is>
-          <t>maa://22468</t>
+          <t>maa://20956, *maa://20830, maa://44703</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C206" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>maa://30673, maa://30672</t>
+          <t>maa://20955</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D207" s="19" t="inlineStr">
         <is>
-          <t>maa://20934, maa://20827, maa://20828</t>
+          <t>maa://39238</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>罗比菈塔</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
@@ -11885,19 +11885,19 @@
       </c>
       <c r="D208" s="19" t="inlineStr">
         <is>
-          <t>maa://20935</t>
+          <t>maa://45261</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>龙舌兰</t>
+          <t>桑葚</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
@@ -11907,19 +11907,19 @@
       </c>
       <c r="D209" s="19" t="inlineStr">
         <is>
-          <t>maa://53354</t>
+          <t>maa://39694</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>羽毛笔</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
@@ -11929,41 +11929,41 @@
       </c>
       <c r="D210" s="19" t="inlineStr">
         <is>
-          <t>maa://28133, maa://25369</t>
+          <t>maa://24636, maa://25778</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D211" s="19" t="inlineStr">
         <is>
-          <t>maa://20956, *maa://20830, maa://44703</t>
+          <t>maa://48261</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>灰毫</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
@@ -11973,19 +11973,19 @@
       </c>
       <c r="D212" s="19" t="inlineStr">
         <is>
-          <t>maa://20955</t>
+          <t>*maa://39157</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
@@ -11995,19 +11995,19 @@
       </c>
       <c r="D213" s="19" t="inlineStr">
         <is>
-          <t>maa://39238</t>
+          <t>*maa://20995</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>罗比菈塔</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
@@ -12017,19 +12017,19 @@
       </c>
       <c r="D214" s="19" t="inlineStr">
         <is>
-          <t>maa://45261</t>
+          <t>maa://26499</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>桑葚</t>
+          <t>布丁</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
@@ -12039,41 +12039,41 @@
       </c>
       <c r="D215" s="19" t="inlineStr">
         <is>
-          <t>maa://39694</t>
+          <t>maa://20858</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>蜜莓</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D216" s="19" t="inlineStr">
         <is>
-          <t>maa://24636, maa://25778</t>
+          <t>maa://39695</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>野鬃</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -12083,19 +12083,19 @@
       </c>
       <c r="D217" s="19" t="inlineStr">
         <is>
-          <t>maa://48261</t>
+          <t>maa://20988</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>灰毫</t>
+          <t>蚀清</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -12105,41 +12105,41 @@
       </c>
       <c r="D218" s="19" t="inlineStr">
         <is>
-          <t>*maa://39157</t>
+          <t>maa://39158</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>NL-5</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D219" s="19" t="inlineStr">
         <is>
-          <t>*maa://20995</t>
+          <t>maa://28187, maa://43531, maa://39520</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>NL-3</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -12149,63 +12149,63 @@
       </c>
       <c r="D220" s="19" t="inlineStr">
         <is>
-          <t>maa://26499</t>
+          <t>maa://20985</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>布丁</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>MN-8</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D221" s="19" t="inlineStr">
         <is>
-          <t>maa://20858</t>
+          <t>maa://20987, *maa://35801</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>蜜莓</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>NL-10</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D222" s="19" t="inlineStr">
         <is>
-          <t>maa://39695</t>
+          <t>*maa://29644, maa://39159</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>野鬃</t>
+          <t>耶拉</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -12215,19 +12215,19 @@
       </c>
       <c r="D223" s="19" t="inlineStr">
         <is>
-          <t>maa://20988</t>
+          <t>maa://30677</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>蚀清</t>
+          <t>极光</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
@@ -12237,19 +12237,19 @@
       </c>
       <c r="D224" s="19" t="inlineStr">
         <is>
-          <t>maa://39158</t>
+          <t>maa://20896</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>NL-5</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -12259,19 +12259,19 @@
       </c>
       <c r="D225" s="19" t="inlineStr">
         <is>
-          <t>maa://28187, maa://43531, maa://39520</t>
+          <t>maa://29058, maa://39140, maa://38723</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>NL-3</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -12281,63 +12281,63 @@
       </c>
       <c r="D226" s="19" t="inlineStr">
         <is>
-          <t>maa://20985</t>
+          <t>*maa://48263</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>九色鹿</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>MN-8</t>
+          <t>IW-3</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D227" s="19" t="inlineStr">
         <is>
-          <t>maa://20987, *maa://35801</t>
+          <t>maa://39160</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>寒芒克洛丝</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>NL-10</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D228" s="19" t="inlineStr">
         <is>
-          <t>*maa://29644, maa://39159</t>
+          <t>maa://49491</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>耶拉</t>
+          <t>夜半</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -12347,19 +12347,19 @@
       </c>
       <c r="D229" s="19" t="inlineStr">
         <is>
-          <t>maa://30677</t>
+          <t>maa://35952</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -12369,63 +12369,63 @@
       </c>
       <c r="D230" s="19" t="inlineStr">
         <is>
-          <t>maa://20896</t>
+          <t>maa://20917</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>IW-EX-1</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D231" s="19" t="inlineStr">
         <is>
-          <t>maa://29058, maa://39140, maa://38723</t>
+          <t>maa://30714, maa://30675</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>令</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D232" s="19" t="inlineStr">
         <is>
-          <t>*maa://48263</t>
+          <t>maa://20922, *maa://32623, maa://34242</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>九色鹿</t>
+          <t>夏栎</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>IW-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
@@ -12435,63 +12435,63 @@
       </c>
       <c r="D233" s="19" t="inlineStr">
         <is>
-          <t>maa://39160</t>
+          <t>maa://32999</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>寒芒克洛丝</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>R8-8</t>
         </is>
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D234" s="19" t="inlineStr">
         <is>
-          <t>maa://49491</t>
+          <t>*maa://30667, maa://30666, *maa://30723, maa://39588</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>夜半</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D235" s="19" t="inlineStr">
         <is>
-          <t>maa://35952</t>
+          <t>maa://62759, maa://62764</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>见行者</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>GA-EX-1</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
@@ -12501,129 +12501,129 @@
       </c>
       <c r="D236" s="19" t="inlineStr">
         <is>
-          <t>maa://20917</t>
+          <t>maa://30512</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>风丸</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>IW-EX-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>maa://30714, maa://30675</t>
+          <t>maa://20870</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>令</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>GA-4</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D238" s="19" t="inlineStr">
         <is>
-          <t>maa://20922, *maa://32623, maa://34242</t>
+          <t>maa://29024</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>夏栎</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D239" s="19" t="inlineStr">
         <is>
-          <t>maa://32999</t>
+          <t>maa://20867, maa://38485, *maa://32202</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>褐果</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>R8-8</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D240" s="19" t="inlineStr">
         <is>
-          <t>*maa://30667, maa://30666, *maa://30723, maa://39588</t>
+          <t>maa://40160</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>海蒂</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D241" s="19" t="inlineStr">
         <is>
-          <t>maa://62759, maa://62764</t>
+          <t>maa://43089</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>见行者</t>
+          <t>洛洛</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>GA-EX-1</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
@@ -12633,261 +12633,261 @@
       </c>
       <c r="D242" s="19" t="inlineStr">
         <is>
-          <t>maa://30512</t>
+          <t>maa://30674</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>风丸</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>7-15</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D243" s="19" t="inlineStr">
         <is>
-          <t>maa://20870</t>
+          <t>maa://28923, maa://28906</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>GA-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>maa://29024</t>
+          <t>maa://42287, maa://45570, maa://42225</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>掠风</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D245" s="19" t="inlineStr">
         <is>
-          <t>maa://20867, maa://38485, *maa://32202</t>
+          <t>maa://39161</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>褐果</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="C246" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D246" s="19" t="inlineStr">
         <is>
-          <t>maa://40160</t>
+          <t>maa://20923, *maa://60577</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>海蒂</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D247" s="19" t="inlineStr">
         <is>
-          <t>maa://43089</t>
+          <t>maa://24093, maa://31559, maa://20924, **maa://49440</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>洛洛</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C248" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D248" s="19" t="inlineStr">
         <is>
-          <t>maa://30674</t>
+          <t>maa://40958, *maa://45067</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>7-15</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>maa://28923, maa://28906</t>
+          <t>maa://20840</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C250" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D250" s="19" t="inlineStr">
         <is>
-          <t>maa://42287, maa://45570, maa://42225</t>
+          <t>maa://20877, *maa://45067, maa://20836, maa://20632</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>掠风</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>11-9</t>
+          <t>S4-1</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D251" s="19" t="inlineStr">
         <is>
-          <t>maa://39161</t>
+          <t>maa://20879, maa://20834</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>埃拉托</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C252" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D252" s="19" t="inlineStr">
         <is>
-          <t>maa://20923, *maa://60577</t>
+          <t>maa://20839</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>濯尘芙蓉</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D253" s="19" t="inlineStr">
         <is>
-          <t>maa://24093, maa://31559, maa://20924, **maa://49440</t>
+          <t>maa://30676</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C254" s="7" t="inlineStr">
@@ -12897,19 +12897,19 @@
       </c>
       <c r="D254" s="19" t="inlineStr">
         <is>
-          <t>maa://40958, *maa://45067</t>
+          <t>maa://31560, maa://20884</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
@@ -12919,63 +12919,63 @@
       </c>
       <c r="D255" s="19" t="inlineStr">
         <is>
-          <t>maa://20840</t>
+          <t>maa://47204</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D256" s="19" t="inlineStr">
         <is>
-          <t>maa://20877, *maa://45067, maa://20836, maa://20632</t>
+          <t>maa://29027</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>星源</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D257" s="19" t="inlineStr">
         <is>
-          <t>maa://20879, maa://20834</t>
+          <t>maa://20977</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>埃拉托</t>
+          <t>承曦格雷伊</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -12985,19 +12985,19 @@
       </c>
       <c r="D258" s="19" t="inlineStr">
         <is>
-          <t>maa://20839</t>
+          <t>maa://39162</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>濯尘芙蓉</t>
+          <t>至简</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>IC-8</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
@@ -13007,41 +13007,41 @@
       </c>
       <c r="D259" s="19" t="inlineStr">
         <is>
-          <t>maa://30676</t>
+          <t>maa://59689</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>晓歌</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D260" s="19" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20884</t>
+          <t>maa://49643</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -13051,41 +13051,41 @@
       </c>
       <c r="D261" s="19" t="inlineStr">
         <is>
-          <t>maa://47204</t>
+          <t>maa://48265</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D262" s="19" t="inlineStr">
         <is>
-          <t>maa://29027</t>
+          <t>*maa://20825, *maa://21445, *maa://35726</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>星源</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -13095,41 +13095,41 @@
       </c>
       <c r="D263" s="19" t="inlineStr">
         <is>
-          <t>maa://20977</t>
+          <t>maa://25769</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>承曦格雷伊</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>RI-9</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D264" s="19" t="inlineStr">
         <is>
-          <t>maa://39162</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>但书</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>MB-EX-1</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
@@ -13139,41 +13139,41 @@
       </c>
       <c r="D265" s="19" t="inlineStr">
         <is>
-          <t>maa://59682</t>
+          <t>maa://20862</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>玛恩纳</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D266" s="19" t="inlineStr">
         <is>
-          <t>maa://22467</t>
+          <t>maa://51881, maa://51630, maa://56588, *maa://55171, maa://51893</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>至简</t>
+          <t>罗小黑</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>IC-8</t>
+          <t>IW-4</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
@@ -13183,19 +13183,19 @@
       </c>
       <c r="D267" s="19" t="inlineStr">
         <is>
-          <t>maa://59689</t>
+          <t>maa://39163</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>晓歌</t>
+          <t>海沫</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C268" s="7" t="inlineStr">
@@ -13205,19 +13205,19 @@
       </c>
       <c r="D268" s="19" t="inlineStr">
         <is>
-          <t>maa://49643</t>
+          <t>maa://29061</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>铅踝</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -13227,85 +13227,85 @@
       </c>
       <c r="D269" s="19" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>maa://20939</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>达格达</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C270" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D270" s="19" t="inlineStr">
         <is>
-          <t>*maa://20825, *maa://21445, *maa://35726</t>
+          <t>maa://39164</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D271" s="19" t="inlineStr">
         <is>
-          <t>maa://25769</t>
+          <t>maa://28133, maa://33394</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>RI-9</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D272" s="19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://42311</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>但书</t>
+          <t>石英</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>DH-4</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
@@ -13315,41 +13315,41 @@
       </c>
       <c r="D273" s="19" t="inlineStr">
         <is>
-          <t>maa://20862</t>
+          <t>maa://41362</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>玛恩纳</t>
+          <t>雪绒</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C274" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D274" s="19" t="inlineStr">
         <is>
-          <t>maa://51881, maa://51630, maa://56588, *maa://55171, maa://51893</t>
+          <t>maa://20978</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>罗小黑</t>
+          <t>子月</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>IW-4</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
@@ -13359,19 +13359,19 @@
       </c>
       <c r="D275" s="19" t="inlineStr">
         <is>
-          <t>maa://39163</t>
+          <t>maa://21002</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>海沫</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C276" s="7" t="inlineStr">
@@ -13381,41 +13381,41 @@
       </c>
       <c r="D276" s="19" t="inlineStr">
         <is>
-          <t>maa://29061</t>
+          <t>*maa://39165</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>铅踝</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>IS-6</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D277" s="19" t="inlineStr">
         <is>
-          <t>maa://20939</t>
+          <t>maa://48267, maa://48266</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>达格达</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C278" s="7" t="inlineStr">
@@ -13425,63 +13425,63 @@
       </c>
       <c r="D278" s="19" t="inlineStr">
         <is>
-          <t>maa://39164</t>
+          <t>maa://29635</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D279" s="19" t="inlineStr">
         <is>
-          <t>maa://28133, maa://33394</t>
+          <t>maa://38296</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>缄默德克萨斯</t>
         </is>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>CB-8</t>
         </is>
       </c>
       <c r="C280" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D280" s="19" t="inlineStr">
         <is>
-          <t>maa://42311</t>
+          <t>maa://20899, maa://46332</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>石英</t>
+          <t>谜图</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>DH-4</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
@@ -13491,19 +13491,19 @@
       </c>
       <c r="D281" s="19" t="inlineStr">
         <is>
-          <t>maa://41362</t>
+          <t>maa://53353</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>雪绒</t>
+          <t>和弦</t>
         </is>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C282" s="7" t="inlineStr">
@@ -13513,41 +13513,41 @@
       </c>
       <c r="D282" s="19" t="inlineStr">
         <is>
-          <t>maa://20978</t>
+          <t>maa://20881</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>子月</t>
+          <t>焰影苇草</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D283" s="19" t="inlineStr">
         <is>
-          <t>maa://21002</t>
+          <t>maa://30710, maa://36845, maa://31558, maa://30668</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>截云</t>
         </is>
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C284" s="7" t="inlineStr">
@@ -13557,63 +13557,63 @@
       </c>
       <c r="D284" s="19" t="inlineStr">
         <is>
-          <t>*maa://39165</t>
+          <t>maa://20902</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>火哨</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>IS-6</t>
+          <t>S4-6</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D285" s="19" t="inlineStr">
         <is>
-          <t>maa://48267, maa://48266</t>
+          <t>maa://29159</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C286" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D286" s="19" t="inlineStr">
         <is>
-          <t>maa://29635</t>
+          <t>maa://25774, maa://28133, maa://22469, **maa://31349</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
@@ -13623,63 +13623,63 @@
       </c>
       <c r="D287" s="19" t="inlineStr">
         <is>
-          <t>maa://38296</t>
+          <t>maa://47882</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>缄默德克萨斯</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>CB-8</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C288" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D288" s="19" t="inlineStr">
         <is>
-          <t>maa://20899, maa://46332</t>
+          <t>maa://32414, maa://32505, maa://39155</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>谜图</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>GA-5</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D289" s="19" t="inlineStr">
         <is>
-          <t>maa://53353</t>
+          <t>maa://45799, maa://57199</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>和弦</t>
+          <t>铎铃</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C290" s="7" t="inlineStr">
@@ -13689,107 +13689,107 @@
       </c>
       <c r="D290" s="19" t="inlineStr">
         <is>
-          <t>maa://20881</t>
+          <t>maa://42312</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>焰影苇草</t>
+          <t>仇白</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D291" s="19" t="inlineStr">
         <is>
-          <t>maa://30710, maa://36845, maa://31558, maa://30668</t>
+          <t>maa://36642, maa://36867, maa://39155</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>截云</t>
+          <t>火龙S黑角</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C292" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D292" s="19" t="inlineStr">
         <is>
-          <t>maa://20902</t>
+          <t>**maa://39166, maa://39167</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>火哨</t>
+          <t>麒麟R夜刀</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D293" s="19" t="inlineStr">
         <is>
-          <t>maa://29159</t>
+          <t>maa://29005, maa://31560</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>休谟斯</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C294" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D294" s="19" t="inlineStr">
         <is>
-          <t>maa://25774, maa://28133, maa://22469, **maa://31349</t>
+          <t>maa://39168</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>摩根</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
@@ -13799,63 +13799,63 @@
       </c>
       <c r="D295" s="19" t="inlineStr">
         <is>
-          <t>maa://47882</t>
+          <t>maa://39169</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>洋灰</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>IW-EX-6</t>
         </is>
       </c>
       <c r="C296" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D296" s="19" t="inlineStr">
         <is>
-          <t>maa://32414, maa://32505, maa://39155</t>
+          <t>maa://39170</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>伊内丝</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>GA-5</t>
+          <t>12-12</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D297" s="19" t="inlineStr">
         <is>
-          <t>maa://45799, maa://57199</t>
+          <t>maa://50280, maa://49642, maa://49660, *maa://50517</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>铎铃</t>
+          <t>玫拉</t>
         </is>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C298" s="7" t="inlineStr">
@@ -13865,85 +13865,85 @@
       </c>
       <c r="D298" s="19" t="inlineStr">
         <is>
-          <t>maa://42312</t>
+          <t>maa://39171</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>仇白</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D299" s="19" t="inlineStr">
         <is>
-          <t>maa://36642, maa://36867, maa://39155</t>
+          <t>maa://27939</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>火龙S黑角</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D300" s="19" t="inlineStr">
         <is>
-          <t>**maa://39166, maa://39167</t>
+          <t>maa://53352</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>麒麟R夜刀</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D301" s="19" t="inlineStr">
         <is>
-          <t>maa://29005, maa://31560</t>
+          <t>maa://29129</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>休谟斯</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C302" s="7" t="inlineStr">
@@ -13953,19 +13953,19 @@
       </c>
       <c r="D302" s="19" t="inlineStr">
         <is>
-          <t>maa://39168</t>
+          <t>maa://36005</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>摩根</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
@@ -13975,19 +13975,19 @@
       </c>
       <c r="D303" s="19" t="inlineStr">
         <is>
-          <t>maa://39169</t>
+          <t>maa://35859</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>洋灰</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>IW-EX-6</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="C304" s="7" t="inlineStr">
@@ -13997,41 +13997,41 @@
       </c>
       <c r="D304" s="19" t="inlineStr">
         <is>
-          <t>maa://39170</t>
+          <t>maa://53348</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>伊内丝</t>
+          <t>隐现</t>
         </is>
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>12-12</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D305" s="19" t="inlineStr">
         <is>
-          <t>maa://50280, maa://49642, maa://49660, *maa://50517</t>
+          <t>**maa://39172</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>玫拉</t>
+          <t>空构</t>
         </is>
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>DM-2</t>
         </is>
       </c>
       <c r="C306" s="7" t="inlineStr">
@@ -14041,41 +14041,41 @@
       </c>
       <c r="D306" s="19" t="inlineStr">
         <is>
-          <t>maa://39171</t>
+          <t>maa://39173</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D307" s="19" t="inlineStr">
         <is>
-          <t>maa://27939</t>
+          <t>maa://25775, *maa://25393</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C308" s="7" t="inlineStr">
@@ -14085,19 +14085,19 @@
       </c>
       <c r="D308" s="19" t="inlineStr">
         <is>
-          <t>maa://53352</t>
+          <t>maa://40161</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -14107,19 +14107,19 @@
       </c>
       <c r="D309" s="19" t="inlineStr">
         <is>
-          <t>maa://29129</t>
+          <t>maa://25367</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
@@ -14129,19 +14129,19 @@
       </c>
       <c r="D310" s="19" t="inlineStr">
         <is>
-          <t>maa://36005</t>
+          <t>*maa://62761</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -14151,19 +14151,19 @@
       </c>
       <c r="D311" s="19" t="inlineStr">
         <is>
-          <t>maa://35859</t>
+          <t>*maa://43090</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>6-12</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C312" s="7" t="inlineStr">
@@ -14173,19 +14173,19 @@
       </c>
       <c r="D312" s="19" t="inlineStr">
         <is>
-          <t>maa://53348</t>
+          <t>maa://28070</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>隐现</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -14195,85 +14195,85 @@
       </c>
       <c r="D313" s="19" t="inlineStr">
         <is>
-          <t>**maa://39172</t>
+          <t>maa://28241</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>空构</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>DM-2</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C314" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D314" s="19" t="inlineStr">
         <is>
-          <t>maa://39173</t>
+          <t>maa://25773, *maa://26088</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D315" s="19" t="inlineStr">
         <is>
-          <t>maa://25775, *maa://25393</t>
+          <t>maa://39239</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C316" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D316" s="19" t="inlineStr">
         <is>
-          <t>maa://40161</t>
+          <t>maa://39692, maa://39810</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
@@ -14283,58 +14283,58 @@
       </c>
       <c r="D317" s="19" t="inlineStr">
         <is>
-          <t>maa://25367</t>
+          <t>*maa://39174</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C318" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D318" s="19" t="inlineStr">
         <is>
-          <t>maa://62761, **maa://62755</t>
+          <t>maa://39175</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D319" s="19" t="inlineStr">
         <is>
-          <t>*maa://43090</t>
+          <t>maa://34867, maa://34715</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
@@ -14349,19 +14349,19 @@
       </c>
       <c r="D320" s="19" t="inlineStr">
         <is>
-          <t>maa://28070</t>
+          <t>maa://39176</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -14371,41 +14371,41 @@
       </c>
       <c r="D321" s="19" t="inlineStr">
         <is>
-          <t>maa://28241</t>
+          <t>maa://42316</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C322" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D322" s="19" t="inlineStr">
         <is>
-          <t>maa://25773, *maa://26088</t>
+          <t>maa://30680</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -14415,129 +14415,129 @@
       </c>
       <c r="D323" s="19" t="inlineStr">
         <is>
-          <t>maa://39239</t>
+          <t>maa://40956</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C324" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D324" s="19" t="inlineStr">
         <is>
-          <t>maa://39692, maa://39810</t>
+          <t>maa://59688</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D325" s="19" t="inlineStr">
         <is>
-          <t>*maa://39174</t>
+          <t>maa://34205, *maa://39541</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C326" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D326" s="19" t="inlineStr">
         <is>
-          <t>maa://39175</t>
+          <t>maa://43092, maa://43093</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D327" s="19" t="inlineStr">
         <is>
-          <t>maa://34867, maa://34715</t>
+          <t>maa://44234</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C328" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D328" s="19" t="inlineStr">
         <is>
-          <t>maa://39176</t>
+          <t>maa://42968, maa://49245</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -14547,19 +14547,19 @@
       </c>
       <c r="D329" s="19" t="inlineStr">
         <is>
-          <t>maa://42316</t>
+          <t>*maa://40162</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C330" s="7" t="inlineStr">
@@ -14569,41 +14569,41 @@
       </c>
       <c r="D330" s="19" t="inlineStr">
         <is>
-          <t>maa://30680</t>
+          <t>maa://37692</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>maa://40956</t>
+          <t>maa://38295, maa://49332</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C332" s="7" t="inlineStr">
@@ -14613,63 +14613,63 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>maa://59688</t>
+          <t>maa://32417</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>maa://34205, *maa://39541</t>
+          <t>maa://32419</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C334" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>maa://43092, maa://43093</t>
+          <t>maa://32416</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
@@ -14679,41 +14679,41 @@
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>maa://44234</t>
+          <t>maa://45800</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>maa://42968, maa://49245</t>
+          <t>maa://32647, maa://32415, maa://34677, maa://32892, maa://32653, maa://61839</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -14723,19 +14723,19 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>*maa://40162</t>
+          <t>maa://32420</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
@@ -14745,85 +14745,85 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>maa://37692</t>
+          <t>maa://35606</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>maa://30671, maa://30669, maa://37275, *maa://32410, maa://41605</t>
+          <t>maa://34716</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>maa://38295, maa://49332</t>
+          <t>maa://39179</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>maa://32417</t>
+          <t>maa://34865, maa://34717, *maa://45066</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C342" s="7" t="inlineStr">
@@ -14833,41 +14833,41 @@
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>maa://32419</t>
+          <t>maa://39180</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>maa://32416</t>
+          <t>maa://45834, maa://45833</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">
@@ -14877,63 +14877,63 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>maa://45800</t>
+          <t>maa://39181</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892, maa://32653, maa://61839</t>
+          <t>maa://36868, maa://35996, maa://47349</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>maa://32420</t>
+          <t>maa://49696, maa://49695, maa://49758, *maa://59402, *maa://52357</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -14943,63 +14943,63 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>maa://35606</t>
+          <t>maa://36647</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>maa://34716</t>
+          <t>maa://42299, maa://42224</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>maa://39179</t>
+          <t>maa://49648, *maa://49662</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C350" s="7" t="inlineStr">
@@ -15009,63 +15009,63 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>maa://34865, maa://34717, *maa://45066</t>
+          <t>maa://36646, maa://36845, maa://51007</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>maa://39180</t>
+          <t>maa://36645, maa://36841, maa://37484, maa://37858, *maa://56268, maa://40489</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>maa://45834, maa://45833</t>
+          <t>maa://42635, maa://50629, maa://48859</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
@@ -15075,63 +15075,63 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>maa://39181</t>
+          <t>maa://39183</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C354" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>maa://36868, maa://35996, maa://47349</t>
+          <t>maa://39184</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>maa://49696, maa://49695, maa://49758, *maa://59402, *maa://52357</t>
+          <t>maa://40957, maa://44635, maa://48026, maa://41035, maa://44660, maa://41128, *maa://60251</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C356" s="7" t="inlineStr">
@@ -15141,107 +15141,107 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>maa://36647</t>
+          <t>maa://40164</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>maa://42299, maa://42224</t>
+          <t>maa://48268</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>maa://49648, *maa://49662</t>
+          <t>maa://40165</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>maa://36646, maa://36845, maa://51007</t>
+          <t>maa://45798</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>maa://36645, maa://36841, maa://37484, maa://37858, *maa://56268, maa://40489</t>
+          <t>maa://42331</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
@@ -15251,85 +15251,85 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>maa://42635, maa://50629, maa://48859</t>
+          <t>maa://42333, maa://50518, maa://41977</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>maa://39183</t>
+          <t>maa://42338, maa://41976</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>maa://39184</t>
+          <t>maa://41110, maa://45605</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>maa://40957, maa://44635, maa://48026, maa://41035, maa://44660, maa://41128, *maa://60251</t>
+          <t>maa://42343</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
@@ -15339,41 +15339,41 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>maa://40164</t>
+          <t>maa://43095</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>maa://48268</t>
+          <t>maa://44233, maa://45570</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
@@ -15383,19 +15383,19 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>maa://40165</t>
+          <t>maa://43097</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C368" s="7" t="inlineStr">
@@ -15405,107 +15405,107 @@
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>maa://45798</t>
+          <t>maa://43875</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>maa://42331</t>
+          <t>maa://42970, maa://44745, *maa://45952, *maa://44896</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>maa://42333, maa://50518, maa://41977</t>
+          <t>maa://44389</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>maa://42338, maa://41976</t>
+          <t>maa://59690</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>maa://41110, maa://45605</t>
+          <t>maa://48113</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
@@ -15515,19 +15515,19 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>maa://42343</t>
+          <t>maa://45807</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C374" s="7" t="inlineStr">
@@ -15537,19 +15537,19 @@
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>maa://43095</t>
+          <t>maa://50552</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
@@ -15559,19 +15559,19 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>maa://44233, maa://45570</t>
+          <t>*maa://47175, maa://47174</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C376" s="7" t="inlineStr">
@@ -15581,19 +15581,19 @@
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>maa://43097</t>
+          <t>maa://47023</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
@@ -15603,14 +15603,14 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>maa://43872</t>
+          <t>**maa://48618</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>死芒</t>
         </is>
       </c>
       <c r="B378" s="6" t="inlineStr">
@@ -15620,188 +15620,188 @@
       </c>
       <c r="C378" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>*maa://53307</t>
+          <t>maa://59533, maa://59577</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>骋风</t>
         </is>
       </c>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>maa://43875</t>
+          <t>maa://51907, maa://51908</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>阿兰娜</t>
         </is>
       </c>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>maa://42970, maa://44745, *maa://45952, *maa://44896</t>
+          <t>**maa://59691</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>信仰搅拌机</t>
         </is>
       </c>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>maa://44389</t>
+          <t>maa://51898, maa://57241</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>特克诺</t>
+          <t>蕾缪安</t>
         </is>
       </c>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>13-13</t>
         </is>
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>maa://59690</t>
+          <t>maa://51880, maa://56651, maa://51878</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>新约能天使</t>
         </is>
       </c>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>GA-EX-5</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>maa://48113</t>
+          <t>maa://51872, maa://51876, maa://51873, maa://62047, maa://63228</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>酒神</t>
         </is>
       </c>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>maa://45807</t>
+          <t>maa://59493, maa://60449</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>录武官</t>
         </is>
       </c>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>HS-5</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>maa://50552</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="7" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>司霆惊蛰</t>
         </is>
       </c>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>DV-7</t>
         </is>
       </c>
       <c r="C386" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>*maa://47175, maa://47174</t>
+          <t>maa://62756</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1446,7 +1446,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.30 14:18:05</t>
+          <t>更新日期：2025.08.02 13:27:24</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="M12" s="15" t="n"/>
@@ -4656,12 +4656,12 @@
       </c>
       <c r="W32" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X32" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Y32" s="15" t="n"/>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="AA35" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB35" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC35" s="15" t="n"/>
@@ -5192,12 +5192,12 @@
       </c>
       <c r="AA36" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB36" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC36" s="15" t="n"/>
@@ -5490,12 +5490,12 @@
       </c>
       <c r="S39" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T39" s="18" t="inlineStr">
         <is>
-          <t>maa://47079, *maa://45788, *maa://45790</t>
+          <t>maa://47079, *maa://45790</t>
         </is>
       </c>
       <c r="U39" s="15" t="n"/>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="AE40" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF40" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AG40" s="12" t="n"/>
@@ -6975,7 +6975,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.07.30 14:18:05</t>
+          <t>更新日期：2025.08.02 13:27:24</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="D108" s="19" t="inlineStr">
         <is>
-          <t>maa://25018, maa://51881, maa://25776, maa://28361, maa://25772, *maa://56588, *maa://45194, *maa://25161, *maa://32653</t>
+          <t>maa://51881, maa://25018, maa://25776, maa://28361, maa://25772, *maa://56588, *maa://45194, *maa://32653, *maa://25161</t>
         </is>
       </c>
     </row>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="D305" s="19" t="inlineStr">
         <is>
-          <t>maa://50280, maa://49642, *maa://49660</t>
+          <t>maa://50280, maa://49642, maa://49660</t>
         </is>
       </c>
     </row>
@@ -14304,12 +14304,12 @@
       </c>
       <c r="C318" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D318" s="19" t="inlineStr">
         <is>
-          <t>maa://62761</t>
+          <t>**maa://62755, maa://62761</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1449,7 +1449,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.08 13:32:35</t>
+          <t>更新日期：2025.08.09 13:24:58</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1783,12 +1783,12 @@
       </c>
       <c r="S10" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="T10" s="18" t="inlineStr">
         <is>
-          <t>maa://27395, maa://22755, **maa://63521</t>
+          <t>maa://27395, maa://22755</t>
         </is>
       </c>
       <c r="U10" s="15" t="n"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="X21" s="18" t="inlineStr">
         <is>
-          <t>maa://20110, maa://34946</t>
+          <t>maa://34946, maa://20110</t>
         </is>
       </c>
       <c r="Y21" s="15" t="n"/>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="AE40" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AF40" s="15" t="inlineStr">
         <is>
-          <t>maa://64205</t>
+          <t>maa://64107, maa://64205</t>
         </is>
       </c>
       <c r="AG40" s="12" t="n"/>
@@ -7040,7 +7040,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.08 13:32:35</t>
+          <t>更新日期：2025.08.09 13:24:58</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -15491,12 +15491,12 @@
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>maa://63883</t>
+          <t>maa://63883, *maa://64045</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>**maa://64972</t>
+          <t>*maa://64972</t>
         </is>
       </c>
       <c r="I7" s="15" t="n"/>
@@ -1449,7 +1449,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.22 13:21:00</t>
+          <t>更新日期：2025.08.25 13:23:23</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1913,12 +1913,12 @@
       </c>
       <c r="S11" s="15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T11" s="18" t="inlineStr">
         <is>
-          <t>maa://22747, maa://22501, maa://45521</t>
+          <t>maa://22747, maa://22501, maa://45521, ***maa://64808</t>
         </is>
       </c>
       <c r="U11" s="15" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="AF28" s="18" t="inlineStr">
         <is>
-          <t>maa://36660, ***maa://65700</t>
+          <t>maa://36660, **maa://65700</t>
         </is>
       </c>
       <c r="AG28" s="12" t="n"/>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="S30" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T30" s="18" t="inlineStr">
         <is>
-          <t>*maa://32940, maa://24388</t>
+          <t>maa://24388</t>
         </is>
       </c>
       <c r="U30" s="15" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="O32" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P32" s="18" t="inlineStr">
         <is>
-          <t>maa://26203</t>
+          <t>maa://26203, ***maa://56429</t>
         </is>
       </c>
       <c r="Q32" s="15" t="n"/>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="AF40" s="15" t="inlineStr">
         <is>
-          <t>maa://64205, *maa://65283</t>
+          <t>maa://64205, maa://65283</t>
         </is>
       </c>
       <c r="AG40" s="12" t="n"/>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>maa://27410, maa://29661, *maa://28038, *maa://56236</t>
+          <t>maa://27410, maa://29661, maa://56236, *maa://28038</t>
         </is>
       </c>
       <c r="I47" s="15" t="n"/>
@@ -7040,7 +7040,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.08.22 13:21:00</t>
+          <t>更新日期：2025.08.25 13:23:23</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8720,7 +8720,7 @@
       </c>
       <c r="D61" s="19" t="inlineStr">
         <is>
-          <t>maa://20841, maa://24093, maa://31559, maa://20924, *maa://25777, *maa://20631</t>
+          <t>maa://20841, maa://31559, maa://24093, maa://20924, *maa://25777, *maa://20631</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="D174" s="19" t="inlineStr">
         <is>
-          <t>maa://59681, *maa://64200</t>
+          <t>maa://59681, maa://64200</t>
         </is>
       </c>
     </row>
@@ -12966,7 +12966,7 @@
       </c>
       <c r="D254" s="19" t="inlineStr">
         <is>
-          <t>maa://24093, maa://31559, maa://20924</t>
+          <t>maa://31559, maa://24093, maa://20924</t>
         </is>
       </c>
     </row>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>maa://42970, maa://44745</t>
+          <t>*maa://42970, maa://44745</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1449,7 +1449,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.09.26 13:19:42</t>
+          <t>更新日期：2025.09.27 13:18:55</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="L14" s="18" t="inlineStr">
         <is>
-          <t>maa://39841, maa://26245, maa://36682, maa://21288</t>
+          <t>maa://39841, maa://36682, maa://26245, maa://21288</t>
         </is>
       </c>
       <c r="M14" s="15" t="n"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P14" s="18" t="inlineStr">
         <is>
-          <t>maa://23250, *maa://20107, *maa://22772, **maa://68732</t>
+          <t>maa://23250, *maa://20107, *maa://22772, *maa://68732</t>
         </is>
       </c>
       <c r="Q14" s="15" t="n"/>
@@ -7124,7 +7124,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.09.26 13:19:42</t>
+          <t>更新日期：2025.09.27 13:18:55</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="H7" s="18" t="inlineStr">
         <is>
-          <t>maa://22763, maa://64972</t>
+          <t>*maa://22763, maa://64972</t>
         </is>
       </c>
       <c r="I7" s="15" t="n"/>
@@ -1449,7 +1449,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.03 13:19:12</t>
+          <t>更新日期：2025.10.04 13:18:25</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="P33" s="18" t="inlineStr">
         <is>
-          <t>maa://21956, maa://69135</t>
+          <t>maa://21956, *maa://69135</t>
         </is>
       </c>
       <c r="Q33" s="15" t="n"/>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>*maa://22525, maa://21284</t>
+          <t>maa://21284</t>
         </is>
       </c>
       <c r="I43" s="15" t="n"/>
@@ -7120,7 +7120,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.03 13:19:12</t>
+          <t>更新日期：2025.10.04 13:18:25</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -7834,7 +7834,7 @@
       </c>
       <c r="D22" s="19" t="inlineStr">
         <is>
-          <t>maa://20948, maa://30844, *maa://63387</t>
+          <t>maa://20948, maa://30844, maa://63387</t>
         </is>
       </c>
       <c r="F22" s="18" t="n"/>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="D56" s="19" t="inlineStr">
         <is>
-          <t>maa://44235, maa://45604, maa://20961, maa://20910</t>
+          <t>maa://44235, maa://45604, *maa://20961, maa://20910</t>
         </is>
       </c>
     </row>
@@ -16280,7 +16280,7 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>maa://51872, maa://51876, *maa://63228, maa://51873, *maa://62047</t>
+          <t>maa://51872, maa://51876, *maa://63228, maa://51873, maa://62047</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -998,7 +998,7 @@
       </c>
       <c r="T4" s="18" t="inlineStr">
         <is>
-          <t>maa://27295, maa://32509, maa://31008, maa://22754, *maa://70489</t>
+          <t>maa://27295, maa://32509, maa://31008, maa://22754, maa://70489</t>
         </is>
       </c>
       <c r="U4" s="15" t="n"/>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="AB5" s="18" t="inlineStr">
         <is>
-          <t>maa://29863, ***maa://26013</t>
+          <t>maa://29863, **maa://26013</t>
         </is>
       </c>
       <c r="AC5" s="15" t="n"/>
@@ -1449,7 +1449,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.09 13:20:20</t>
+          <t>更新日期：2025.10.11 13:18:19</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="L9" s="18" t="inlineStr">
         <is>
-          <t>maa://22762, *maa://39552</t>
+          <t>maa://22762, maa://39552</t>
         </is>
       </c>
       <c r="M9" s="15" t="n"/>
@@ -2157,12 +2157,12 @@
       </c>
       <c r="O13" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" s="18" t="inlineStr">
         <is>
-          <t>maa://22676, maa://22583</t>
+          <t>maa://22676, maa://22583, *maa://22500</t>
         </is>
       </c>
       <c r="Q13" s="15" t="n"/>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="L22" s="18" t="inlineStr">
         <is>
-          <t>*maa://27127, *maa://22751, maa://66865</t>
+          <t>maa://27127, *maa://22751, maa://66865</t>
         </is>
       </c>
       <c r="M22" s="15" t="n"/>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="AE46" s="15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF46" s="15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://70759</t>
         </is>
       </c>
       <c r="AG46" s="12" t="n"/>
@@ -7128,7 +7128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB418"/>
+  <dimension ref="A1:AB420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
@@ -7170,7 +7170,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.09 13:20:20</t>
+          <t>更新日期：2025.10.11 13:18:19</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>*maa://20849, *maa://28758, maa://29036, maa://65357, *maa://42172, maa://30285</t>
+          <t>*maa://20849, *maa://28758, maa://65357, maa://29036, *maa://42172, *maa://30285</t>
         </is>
       </c>
       <c r="F27" s="18" t="n"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="D168" s="19" t="inlineStr">
         <is>
-          <t>maa://20975, *maa://47950, maa://30806</t>
+          <t>maa://20975, maa://47950, maa://30806</t>
         </is>
       </c>
     </row>
@@ -11881,12 +11881,12 @@
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D199" s="19" t="inlineStr">
         <is>
-          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://51066, maa://63024</t>
+          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://51066, maa://63024, *maa://70161</t>
         </is>
       </c>
     </row>
@@ -13074,7 +13074,7 @@
       </c>
       <c r="D253" s="19" t="inlineStr">
         <is>
-          <t>maa://42287, maa://45570, *maa://60678, maa://42225</t>
+          <t>maa://42287, maa://45570, maa://60678, maa://42225</t>
         </is>
       </c>
     </row>
@@ -14511,34 +14511,34 @@
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>GA-3</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D319" s="19" t="inlineStr">
         <is>
-          <t>maa://40161</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C320" s="7" t="inlineStr">
@@ -14548,7 +14548,7 @@
       </c>
       <c r="D320" s="19" t="inlineStr">
         <is>
-          <t>maa://25367</t>
+          <t>maa://40161</t>
         </is>
       </c>
     </row>
@@ -14560,51 +14560,51 @@
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D321" s="19" t="inlineStr">
         <is>
-          <t>*maa://62755, maa://62761</t>
+          <t>maa://25367</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C322" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D322" s="19" t="inlineStr">
         <is>
-          <t>maa://43090</t>
+          <t>*maa://62755, maa://62761</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
@@ -14614,19 +14614,19 @@
       </c>
       <c r="D323" s="19" t="inlineStr">
         <is>
-          <t>maa://28070</t>
+          <t>maa://43090</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C324" s="7" t="inlineStr">
@@ -14636,19 +14636,19 @@
       </c>
       <c r="D324" s="19" t="inlineStr">
         <is>
-          <t>maa://28241</t>
+          <t>maa://28070</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="D325" s="19" t="inlineStr">
         <is>
-          <t>maa://25773</t>
+          <t>maa://28241</t>
         </is>
       </c>
     </row>
@@ -14670,7 +14670,7 @@
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C326" s="7" t="inlineStr">
@@ -14680,63 +14680,63 @@
       </c>
       <c r="D326" s="19" t="inlineStr">
         <is>
-          <t>maa://39239</t>
+          <t>maa://25773</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D327" s="19" t="inlineStr">
         <is>
-          <t>maa://39692, *maa://39810</t>
+          <t>maa://39239</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C328" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D328" s="19" t="inlineStr">
         <is>
-          <t>maa://39174</t>
+          <t>maa://39692, *maa://39810</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -14746,63 +14746,63 @@
       </c>
       <c r="D329" s="19" t="inlineStr">
         <is>
-          <t>maa://39175</t>
+          <t>maa://39174</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D330" s="19" t="inlineStr">
         <is>
-          <t>maa://34715, maa://34867</t>
+          <t>maa://39175</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>maa://39176</t>
+          <t>maa://34715, maa://34867</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C332" s="7" t="inlineStr">
@@ -14812,19 +14812,19 @@
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>maa://42316</t>
+          <t>maa://39176</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -14834,19 +14834,19 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>maa://30680</t>
+          <t>maa://42316</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C334" s="7" t="inlineStr">
@@ -14856,63 +14856,63 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>maa://40956</t>
+          <t>maa://30680</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>跃跃</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://40956</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>折光</t>
+          <t>跃跃</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>maa://67818</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>折光</t>
         </is>
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -14922,29 +14922,29 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>maa://59688</t>
+          <t>maa://67818</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>maa://34205, **maa://39541</t>
+          <t>maa://59688</t>
         </is>
       </c>
     </row>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
@@ -14966,51 +14966,51 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>maa://43092, maa://43093</t>
+          <t>maa://34205, **maa://39541</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>maa://44234</t>
+          <t>maa://43092, maa://43093</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>maa://42968, maa://49245</t>
+          <t>maa://44234</t>
         </is>
       </c>
     </row>
@@ -15022,29 +15022,29 @@
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>ZT-8</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>maa://67275</t>
+          <t>maa://42968, maa://49245</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>ZT-8</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
@@ -15054,19 +15054,19 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>maa://40162</t>
+          <t>maa://67275</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">
@@ -15076,107 +15076,107 @@
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>maa://37692</t>
+          <t>maa://40162</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>*maa://30671, maa://30669, *maa://37275, *maa://41605</t>
+          <t>maa://37692</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>温米</t>
+          <t>锏</t>
         </is>
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>6-11</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>maa://67817</t>
+          <t>*maa://30671, maa://30669, *maa://37275, *maa://41605</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>温米</t>
         </is>
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>6-11</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>maa://38295, *maa://49332</t>
+          <t>maa://67817</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>maa://32417</t>
+          <t>maa://38295, *maa://49332</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
@@ -15186,19 +15186,19 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>maa://32419</t>
+          <t>maa://32417</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C350" s="7" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>maa://32416</t>
+          <t>maa://32419</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -15230,63 +15230,63 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>maa://45800</t>
+          <t>maa://32416</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892, *maa://32653, *maa://61839, *maa://61275</t>
+          <t>maa://45800</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>maa://32420</t>
+          <t>maa://32647, maa://32415, maa://34677, maa://32892, *maa://32653, *maa://61839, *maa://61275</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C354" s="7" t="inlineStr">
@@ -15296,19 +15296,19 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>maa://35606</t>
+          <t>maa://32420</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
@@ -15318,19 +15318,19 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>maa://34716</t>
+          <t>maa://35606</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C356" s="7" t="inlineStr">
@@ -15340,117 +15340,117 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>maa://39179</t>
+          <t>maa://34716</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>maa://34865, maa://34717</t>
+          <t>maa://39179</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>maa://39180</t>
+          <t>maa://34865, maa://34717</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B359" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C359" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>maa://45834, *maa://45833</t>
+          <t>maa://39180</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>maa://39181</t>
+          <t>maa://45834, *maa://45833</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>maa://36868, maa://35996, maa://47349</t>
+          <t>maa://39181</t>
         </is>
       </c>
     </row>
@@ -15462,73 +15462,73 @@
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>maa://49696, maa://49695, maa://49758, *maa://52357</t>
+          <t>maa://36868, maa://35996, maa://47349</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>maa://36647</t>
+          <t>maa://49696, maa://49695, maa://49758, *maa://52357</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>maa://42299, *maa://42224</t>
+          <t>maa://36647</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>maa://49648, *maa://49662</t>
+          <t>maa://42299, *maa://42224</t>
         </is>
       </c>
     </row>
@@ -15550,95 +15550,95 @@
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>maa://36646, maa://36845, maa://51007</t>
+          <t>maa://49648, *maa://49662</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>maa://36645, maa://36841, maa://37484, maa://37858</t>
+          <t>maa://36646, maa://36845, maa://51007</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>maa://42635, *maa://50629, *maa://48859</t>
+          <t>maa://36645, maa://36841, maa://37484, maa://37858</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>maa://39183</t>
+          <t>maa://42635, *maa://50629, *maa://48859</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C370" s="7" t="inlineStr">
@@ -15648,107 +15648,107 @@
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>maa://39184</t>
+          <t>maa://39183</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>maa://40957, maa://48026, maa://44635, maa://41035, *maa://60251, maa://44660, *maa://41128</t>
+          <t>maa://39184</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>maa://40164</t>
+          <t>maa://40957, maa://48026, maa://44635, maa://41035, *maa://60251, maa://44660, *maa://41128</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>妮芙</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>14-7</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>maa://63883, maa://64045</t>
+          <t>maa://40164</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>妮芙</t>
         </is>
       </c>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>14-7</t>
         </is>
       </c>
       <c r="C374" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>maa://48268</t>
+          <t>maa://63883, maa://64045</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
@@ -15758,41 +15758,41 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>maa://40165</t>
+          <t>maa://48268</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>娜仁图亚</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>WB-6</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://40165</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>娜仁图亚</t>
         </is>
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>WB-6</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
@@ -15802,19 +15802,19 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>maa://45798</t>
+          <t>maa://70756</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C378" s="7" t="inlineStr">
@@ -15824,107 +15824,107 @@
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>maa://42331</t>
+          <t>maa://45798</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>maa://42333, *maa://50518, *maa://41977</t>
+          <t>maa://42331</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>maa://42338</t>
+          <t>maa://42333, *maa://50518, *maa://41977</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>maa://41110, *maa://45605</t>
+          <t>maa://42338</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>maa://42343</t>
+          <t>maa://41110, *maa://45605</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
@@ -15934,63 +15934,63 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>maa://43095</t>
+          <t>maa://42343</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>maa://44233, maa://45570</t>
+          <t>maa://43095</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>maa://43097</t>
+          <t>maa://44233, maa://45570</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="7" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C386" s="7" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>maa://43872</t>
+          <t>maa://43097</t>
         </is>
       </c>
     </row>
@@ -16012,7 +16012,7 @@
       </c>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
@@ -16022,19 +16022,19 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>maa://53307</t>
+          <t>maa://43872</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="7" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B388" s="6" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C388" s="7" t="inlineStr">
@@ -16044,63 +16044,63 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>maa://43875</t>
+          <t>maa://53307</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>*maa://42970, maa://44745, *maa://44896</t>
+          <t>maa://43875</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="7" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>maa://44389</t>
+          <t>*maa://42970, maa://44745, *maa://44896</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>特克诺</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
@@ -16110,19 +16110,19 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>maa://59690</t>
+          <t>maa://44389</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="7" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C392" s="7" t="inlineStr">
@@ -16132,19 +16132,19 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>maa://48113</t>
+          <t>maa://59690</t>
         </is>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c r="A393" s="13" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B393" s="20" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C393" s="13" t="inlineStr">
@@ -16154,19 +16154,19 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>maa://45807</t>
+          <t>maa://48113</t>
         </is>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c r="A394" s="13" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B394" s="20" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C394" s="13" t="inlineStr">
@@ -16176,19 +16176,19 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://50552</t>
+          <t>maa://45807</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="13" t="inlineStr">
         <is>
-          <t>烛煌</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B395" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C395" s="13" t="inlineStr">
@@ -16198,151 +16198,151 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>maa://63890</t>
+          <t>maa://50552</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="13" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>烛煌</t>
         </is>
       </c>
       <c r="B396" s="13" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C396" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>*maa://47175, maa://47174</t>
+          <t>maa://63890</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="13" t="inlineStr">
         <is>
-          <t>隐德来希</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B397" s="13" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C397" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>maa://47023</t>
+          <t>*maa://47175, maa://47174</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="13" t="inlineStr">
         <is>
-          <t>水灯心</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B398" s="13" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C398" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://47023</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="13" t="inlineStr">
         <is>
-          <t>钼铅</t>
+          <t>水灯心</t>
         </is>
       </c>
       <c r="B399" s="13" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C399" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>maa://48618</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="13" t="inlineStr">
         <is>
-          <t>死芒</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B400" s="13" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C400" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>maa://59533, maa://59577</t>
+          <t>maa://48618</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="13" t="inlineStr">
         <is>
-          <t>骋风</t>
+          <t>死芒</t>
         </is>
       </c>
       <c r="B401" s="13" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C401" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>maa://51908</t>
+          <t>maa://59533, maa://59577</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="13" t="inlineStr">
         <is>
-          <t>阿兰娜</t>
+          <t>骋风</t>
         </is>
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
@@ -16352,151 +16352,151 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>maa://59691</t>
+          <t>maa://51908</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="13" t="inlineStr">
         <is>
-          <t>信仰搅拌机</t>
+          <t>阿兰娜</t>
         </is>
       </c>
       <c r="B403" s="13" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C403" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>maa://51898, maa://57241</t>
+          <t>maa://59691</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="13" t="inlineStr">
         <is>
-          <t>蕾缪安</t>
+          <t>信仰搅拌机</t>
         </is>
       </c>
       <c r="B404" s="13" t="inlineStr">
         <is>
-          <t>13-13</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C404" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>maa://51880, maa://56651, maa://51878</t>
+          <t>maa://51898, maa://57241</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="13" t="inlineStr">
         <is>
-          <t>新约能天使</t>
+          <t>蕾缪安</t>
         </is>
       </c>
       <c r="B405" s="13" t="inlineStr">
         <is>
-          <t>GA-EX-5</t>
+          <t>13-13</t>
         </is>
       </c>
       <c r="C405" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>maa://51872, maa://51876, *maa://63228, maa://51873, maa://62047</t>
+          <t>maa://51880, maa://56651, maa://51878</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="13" t="inlineStr">
         <is>
-          <t>Miss.Christine</t>
+          <t>新约能天使</t>
         </is>
       </c>
       <c r="B406" s="13" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>GA-EX-5</t>
         </is>
       </c>
       <c r="C406" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>maa://67814</t>
+          <t>maa://51872, maa://51876, *maa://63228, maa://51873, maa://62047</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="13" t="inlineStr">
         <is>
-          <t>酒神</t>
+          <t>Miss.Christine</t>
         </is>
       </c>
       <c r="B407" s="13" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>DM-7</t>
         </is>
       </c>
       <c r="C407" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>maa://60449, maa://59493</t>
+          <t>maa://67814</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="13" t="inlineStr">
         <is>
-          <t>录武官</t>
+          <t>酒神</t>
         </is>
       </c>
       <c r="B408" s="13" t="inlineStr">
         <is>
-          <t>HS-5</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C408" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>maa://67815</t>
+          <t>maa://60449, maa://59493</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="13" t="inlineStr">
         <is>
-          <t>司霆惊蛰</t>
+          <t>录武官</t>
         </is>
       </c>
       <c r="B409" s="13" t="inlineStr">
         <is>
-          <t>DV-7</t>
+          <t>HS-5</t>
         </is>
       </c>
       <c r="C409" s="13" t="inlineStr">
@@ -16506,19 +16506,19 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>maa://62756</t>
+          <t>maa://67815</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="13" t="inlineStr">
         <is>
-          <t>吉星</t>
+          <t>司霆惊蛰</t>
         </is>
       </c>
       <c r="B410" s="13" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>DV-7</t>
         </is>
       </c>
       <c r="C410" s="13" t="inlineStr">
@@ -16528,63 +16528,63 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>maa://67816</t>
+          <t>maa://62756</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="13" t="inlineStr">
         <is>
-          <t>遥</t>
+          <t>吉星</t>
         </is>
       </c>
       <c r="B411" s="13" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C411" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>maa://64040, maa://52505, *maa://66377</t>
+          <t>maa://67816</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="13" t="inlineStr">
         <is>
-          <t>祐天寺若麦</t>
+          <t>遥</t>
         </is>
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>ZT-4</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C412" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>maa://67090</t>
+          <t>maa://64040, maa://52505, *maa://66377</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="13" t="inlineStr">
         <is>
-          <t>八幡海铃</t>
+          <t>祐天寺若麦</t>
         </is>
       </c>
       <c r="B413" s="13" t="inlineStr">
         <is>
-          <t>BB-7</t>
+          <t>ZT-4</t>
         </is>
       </c>
       <c r="C413" s="13" t="inlineStr">
@@ -16594,117 +16594,161 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>maa://67388</t>
+          <t>maa://67090</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="13" t="inlineStr">
         <is>
-          <t>若叶睦</t>
+          <t>八幡海铃</t>
         </is>
       </c>
       <c r="B414" s="13" t="inlineStr">
         <is>
-          <t>13-16</t>
+          <t>BB-7</t>
         </is>
       </c>
       <c r="C414" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>maa://67089, maa://67271</t>
+          <t>maa://67388</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="13" t="inlineStr">
         <is>
-          <t>三角初华</t>
+          <t>若叶睦</t>
         </is>
       </c>
       <c r="B415" s="13" t="inlineStr">
         <is>
-          <t>ZT-6</t>
+          <t>13-16</t>
         </is>
       </c>
       <c r="C415" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>maa://67088</t>
+          <t>maa://67089, maa://67271</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="13" t="inlineStr">
         <is>
-          <t>丰川祥子</t>
+          <t>三角初华</t>
         </is>
       </c>
       <c r="B416" s="13" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>ZT-6</t>
         </is>
       </c>
       <c r="C416" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>maa://67087, maa://67268, *maa://67269, *maa://67648</t>
+          <t>maa://67088</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="13" t="inlineStr">
         <is>
-          <t>冬时</t>
+          <t>丰川祥子</t>
         </is>
       </c>
       <c r="B417" s="13" t="inlineStr">
         <is>
-          <t>R8-2</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C417" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://67087, maa://67268, *maa://67269, *maa://67648</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="13" t="inlineStr">
         <is>
+          <t>冬时</t>
+        </is>
+      </c>
+      <c r="B418" s="13" t="inlineStr">
+        <is>
+          <t>R8-2</t>
+        </is>
+      </c>
+      <c r="C418" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="13" t="inlineStr">
+        <is>
           <t>折桠</t>
         </is>
       </c>
-      <c r="B418" s="13" t="inlineStr">
+      <c r="B419" s="13" t="inlineStr">
         <is>
           <t>MB-5</t>
         </is>
       </c>
-      <c r="C418" s="13" t="inlineStr">
+      <c r="C419" s="13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="13" t="inlineStr">
+        <is>
+          <t>真言</t>
+        </is>
+      </c>
+      <c r="B420" s="13" t="inlineStr">
+        <is>
+          <t>FC-5</t>
+        </is>
+      </c>
+      <c r="C420" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>maa://70877</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -142,6 +142,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG79"/>
+  <dimension ref="A1:AG80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="26.25" customWidth="1" style="15" min="1" max="1"/>
@@ -1449,7 +1452,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.31 13:21:33</t>
+          <t>更新日期：2025.11.01 13:26:33</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -3104,7 +3107,7 @@
       </c>
       <c r="X20" s="18" t="inlineStr">
         <is>
-          <t>maa://50085, maa://56241, maa://49976</t>
+          <t>maa://56241, maa://50085, maa://49976</t>
         </is>
       </c>
       <c r="Y20" s="15" t="n"/>
@@ -3603,12 +3606,12 @@
       </c>
       <c r="S24" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="U24" s="15" t="n"/>
@@ -4805,12 +4808,12 @@
       </c>
       <c r="AA33" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB33" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="AC33" s="15" t="n"/>
@@ -5564,8 +5567,22 @@
       <c r="AG39" s="12" t="n"/>
     </row>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>凛御银灰</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" s="12" t="n"/>
       <c r="F40" s="15" t="inlineStr">
         <is>
           <t>战车</t>
@@ -6030,6 +6047,22 @@
         </is>
       </c>
       <c r="U44" s="15" t="n"/>
+      <c r="Z44" s="12" t="inlineStr">
+        <is>
+          <t>溯光星源</t>
+        </is>
+      </c>
+      <c r="AA44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB44" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC44" s="12" t="n"/>
       <c r="AD44" s="15" t="inlineStr">
         <is>
           <t>钼铅</t>
@@ -6669,15 +6702,31 @@
       </c>
       <c r="O55" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q55" s="12" t="n"/>
+      <c r="R55" s="12" t="inlineStr">
+        <is>
+          <t>协律</t>
+        </is>
+      </c>
+      <c r="S55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T55" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U55" s="12" t="n"/>
     </row>
     <row r="56">
       <c r="F56" s="15" t="inlineStr">
@@ -6696,6 +6745,38 @@
         </is>
       </c>
       <c r="I56" s="15" t="n"/>
+      <c r="N56" s="12" t="inlineStr">
+        <is>
+          <t>雪猎</t>
+        </is>
+      </c>
+      <c r="O56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="n"/>
+      <c r="R56" s="12" t="inlineStr">
+        <is>
+          <t>圣聆初雪</t>
+        </is>
+      </c>
+      <c r="S56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T56" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U56" s="12" t="n"/>
     </row>
     <row r="57">
       <c r="F57" s="15" t="inlineStr">
@@ -6849,12 +6930,12 @@
       </c>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>None</t>
         </is>
       </c>
       <c r="I65" s="15" t="n"/>
@@ -7110,6 +7191,24 @@
         </is>
       </c>
       <c r="I79" s="12" t="n"/>
+    </row>
+    <row r="80">
+      <c r="F80" s="12" t="inlineStr">
+        <is>
+          <t>哈蒂娅</t>
+        </is>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="12" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7128,7 +7227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB420"/>
+  <dimension ref="A1:AB430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.5" bestFit="1" customWidth="1" style="18" min="1" max="1"/>
@@ -7170,7 +7269,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.10.31 13:21:33</t>
+          <t>更新日期：2025.11.01 13:26:33</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -7918,7 +8017,7 @@
       </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
-          <t>maa://20876, *maa://63498</t>
+          <t>maa://20876, maa://63498</t>
         </is>
       </c>
       <c r="F23" s="18" t="n"/>
@@ -9539,7 +9638,7 @@
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>红云</t>
+          <t>坚雷</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
@@ -9549,24 +9648,24 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D93" s="19" t="inlineStr">
         <is>
-          <t>maa://20890</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>炎客</t>
+          <t>红云</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>S4-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
@@ -9576,19 +9675,19 @@
       </c>
       <c r="D94" s="19" t="inlineStr">
         <is>
-          <t>maa://20984</t>
+          <t>maa://20890</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>送葬人</t>
+          <t>炎客</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>IW-8</t>
+          <t>S4-3</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
@@ -9598,19 +9697,19 @@
       </c>
       <c r="D95" s="19" t="inlineStr">
         <is>
-          <t>maa://40157</t>
+          <t>maa://20984</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>麦哲伦</t>
+          <t>送葬人</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>IW-8</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
@@ -9620,7 +9719,7 @@
       </c>
       <c r="D96" s="19" t="inlineStr">
         <is>
-          <t>maa://20927</t>
+          <t>maa://40157</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9731,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
@@ -9642,63 +9741,63 @@
       </c>
       <c r="D97" s="19" t="inlineStr">
         <is>
-          <t>maa://20926</t>
+          <t>maa://20927</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>伊桑</t>
+          <t>麦哲伦</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>TW-3</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D98" s="19" t="inlineStr">
         <is>
-          <t>maa://20991, *maa://51015</t>
+          <t>maa://20926</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>微风</t>
+          <t>伊桑</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>TW-3</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D99" s="19" t="inlineStr">
         <is>
-          <t>maa://20967</t>
+          <t>maa://20991, *maa://51015</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>梅</t>
+          <t>微风</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
@@ -9708,19 +9807,19 @@
       </c>
       <c r="D100" s="19" t="inlineStr">
         <is>
-          <t>maa://20929</t>
+          <t>maa://20967</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>拜松</t>
+          <t>梅</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
@@ -9730,51 +9829,51 @@
       </c>
       <c r="D101" s="19" t="inlineStr">
         <is>
-          <t>maa://20852</t>
+          <t>maa://20929</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>槐琥</t>
+          <t>拜松</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D102" s="19" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, maa://20893</t>
+          <t>maa://20852</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>莫斯提马</t>
+          <t>槐琥</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>DM-3</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D103" s="19" t="inlineStr">
         <is>
-          <t>maa://40517</t>
+          <t>maa://45572, maa://27794, maa://20893</t>
         </is>
       </c>
     </row>
@@ -9786,51 +9885,51 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>CB-5</t>
+          <t>DM-3</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D104" s="19" t="inlineStr">
         <is>
-          <t>maa://29094, maa://28904</t>
+          <t>maa://40517</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>苇草</t>
+          <t>莫斯提马</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>CB-5</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D105" s="19" t="inlineStr">
         <is>
-          <t>maa://20966</t>
+          <t>maa://29094, maa://28904</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>布洛卡</t>
+          <t>苇草</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
@@ -9840,73 +9939,73 @@
       </c>
       <c r="D106" s="19" t="inlineStr">
         <is>
-          <t>maa://39143</t>
+          <t>maa://20966</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>安比尔</t>
+          <t>布洛卡</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D107" s="19" t="inlineStr">
         <is>
-          <t>maa://45572, maa://27794, *maa://20843</t>
+          <t>maa://39143</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>灰喉</t>
+          <t>安比尔</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D108" s="19" t="inlineStr">
         <is>
-          <t>maa://20894</t>
+          <t>maa://45572, maa://27794, *maa://20843</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>煌</t>
+          <t>灰喉</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>11-13</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D109" s="19" t="inlineStr">
         <is>
-          <t>maa://51881, maa://25018, maa://25776, maa://28361, maa://25772, maa://56588, *maa://45194, *maa://32653, *maa://25161, *maa://61839, *maa://61275</t>
+          <t>maa://20894</t>
         </is>
       </c>
     </row>
@@ -9918,51 +10017,51 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>11-13</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D110" s="19" t="inlineStr">
         <is>
-          <t>maa://36646, maa://25774, maa://35996, maa://22469, *maa://30668, maa://67286</t>
+          <t>maa://51881, maa://25018, maa://25776, maa://28361, maa://25772, maa://56588, *maa://45194, *maa://32653, *maa://25161, *maa://61839, *maa://61275</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>雪雉</t>
+          <t>煌</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D111" s="19" t="inlineStr">
         <is>
-          <t>maa://45259</t>
+          <t>maa://36646, maa://25774, maa://35996, maa://22469, *maa://30668, maa://67286</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>吽</t>
+          <t>雪雉</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>S2-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
@@ -9972,19 +10071,19 @@
       </c>
       <c r="D112" s="19" t="inlineStr">
         <is>
-          <t>maa://20887</t>
+          <t>maa://45259</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>阿</t>
+          <t>吽</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>S2-4</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
@@ -9994,29 +10093,29 @@
       </c>
       <c r="D113" s="19" t="inlineStr">
         <is>
-          <t>maa://28554</t>
+          <t>maa://20887</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>阿</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>WR-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D114" s="19" t="inlineStr">
         <is>
-          <t>maa://20933, maa://20822</t>
+          <t>maa://28554</t>
         </is>
       </c>
     </row>
@@ -10028,29 +10127,29 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>S6-2</t>
+          <t>WR-9</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D115" s="19" t="inlineStr">
         <is>
-          <t>maa://29037</t>
+          <t>maa://20933, maa://20822</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>惊蛰</t>
+          <t>年</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>S6-2</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
@@ -10060,29 +10159,29 @@
       </c>
       <c r="D116" s="19" t="inlineStr">
         <is>
-          <t>maa://20904</t>
+          <t>maa://29037</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>刻俄柏</t>
+          <t>惊蛰</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>RI-6</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D117" s="19" t="inlineStr">
         <is>
-          <t>maa://20908, maa://35723, maa://38822, *maa://58659</t>
+          <t>maa://20904</t>
         </is>
       </c>
     </row>
@@ -10094,29 +10193,29 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>RI-6</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D118" s="19" t="inlineStr">
         <is>
-          <t>maa://29659, maa://29031</t>
+          <t>maa://20908, maa://35723, maa://38822, *maa://58659</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>清流</t>
+          <t>刻俄柏</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
@@ -10126,95 +10225,95 @@
       </c>
       <c r="D119" s="19" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20940</t>
+          <t>maa://29659, maa://29031</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>宴</t>
+          <t>清流</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D120" s="19" t="inlineStr">
         <is>
-          <t>maa://20986</t>
+          <t>maa://31560, maa://20940</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>柏喙</t>
+          <t>宴</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D121" s="19" t="inlineStr">
         <is>
-          <t>maa://31560, *maa://20851</t>
+          <t>maa://20986</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>慑砂</t>
+          <t>柏喙</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D122" s="19" t="inlineStr">
         <is>
-          <t>maa://20949</t>
+          <t>maa://31560, *maa://20851</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>风笛</t>
+          <t>慑砂</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D123" s="19" t="inlineStr">
         <is>
-          <t>maa://20869, maa://44690</t>
+          <t>maa://20949</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10325,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
@@ -10236,41 +10335,41 @@
       </c>
       <c r="D124" s="19" t="inlineStr">
         <is>
-          <t>maa://29650, maa://45570</t>
+          <t>maa://20869, maa://44690</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>断罪者</t>
+          <t>风笛</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D125" s="19" t="inlineStr">
         <is>
-          <t>maa://20868</t>
+          <t>maa://29650, maa://45570</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>刻刀</t>
+          <t>断罪者</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
@@ -10280,19 +10379,19 @@
       </c>
       <c r="D126" s="19" t="inlineStr">
         <is>
-          <t>maa://20909</t>
+          <t>maa://20868</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>铸铁</t>
+          <t>刻刀</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>DH-3</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
@@ -10302,19 +10401,19 @@
       </c>
       <c r="D127" s="19" t="inlineStr">
         <is>
-          <t>maa://44403</t>
+          <t>maa://20909</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>巫恋</t>
+          <t>铸铁</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>DH-3</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
@@ -10324,29 +10423,29 @@
       </c>
       <c r="D128" s="19" t="inlineStr">
         <is>
-          <t>maa://30501</t>
+          <t>maa://44403</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>傀影</t>
+          <t>巫恋</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D129" s="19" t="inlineStr">
         <is>
-          <t>*maa://20914, maa://20829</t>
+          <t>maa://30501</t>
         </is>
       </c>
     </row>
@@ -10358,7 +10457,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C130" s="7" t="inlineStr">
@@ -10368,19 +10467,19 @@
       </c>
       <c r="D130" s="19" t="inlineStr">
         <is>
-          <t>maa://37484, maa://24611</t>
+          <t>*maa://20914, maa://20829</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>极境</t>
+          <t>傀影</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
@@ -10390,29 +10489,29 @@
       </c>
       <c r="D131" s="19" t="inlineStr">
         <is>
-          <t>maa://24491, *maa://24493</t>
+          <t>maa://37484, maa://24611</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>温蒂</t>
+          <t>极境</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>BI-5</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C132" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D132" s="19" t="inlineStr">
         <is>
-          <t>maa://21422</t>
+          <t>maa://24491, *maa://24493</t>
         </is>
       </c>
     </row>
@@ -10424,7 +10523,7 @@
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>IC-6</t>
+          <t>BI-5</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
@@ -10434,29 +10533,29 @@
       </c>
       <c r="D133" s="19" t="inlineStr">
         <is>
-          <t>maa://30719</t>
+          <t>maa://21422</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>温蒂</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>DM-3</t>
+          <t>IC-6</t>
         </is>
       </c>
       <c r="C134" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D134" s="19" t="inlineStr">
         <is>
-          <t>maa://20837, *maa://37666</t>
+          <t>maa://30719</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10567,7 @@
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>DM-3</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
@@ -10478,63 +10577,63 @@
       </c>
       <c r="D135" s="19" t="inlineStr">
         <is>
-          <t>maa://29023, *maa://39515</t>
+          <t>maa://20837, *maa://37666</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>月禾</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>DM-7</t>
         </is>
       </c>
       <c r="C136" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D136" s="19" t="inlineStr">
         <is>
-          <t>maa://39146</t>
+          <t>maa://29023, *maa://39515</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>波登可</t>
+          <t>石棉</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D137" s="19" t="inlineStr">
         <is>
-          <t>maa://20856</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>苦艾</t>
+          <t>月禾</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C138" s="7" t="inlineStr">
@@ -10544,19 +10643,19 @@
       </c>
       <c r="D138" s="19" t="inlineStr">
         <is>
-          <t>maa://20913</t>
+          <t>maa://39146</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>莱恩哈特</t>
+          <t>波登可</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
@@ -10566,19 +10665,19 @@
       </c>
       <c r="D139" s="19" t="inlineStr">
         <is>
-          <t>maa://41856</t>
+          <t>maa://20856</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>早露</t>
+          <t>苦艾</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C140" s="7" t="inlineStr">
@@ -10588,19 +10687,19 @@
       </c>
       <c r="D140" s="19" t="inlineStr">
         <is>
-          <t>maa://29025</t>
+          <t>maa://20913</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>卡达</t>
+          <t>莱恩哈特</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
@@ -10610,19 +10709,19 @@
       </c>
       <c r="D141" s="19" t="inlineStr">
         <is>
-          <t>maa://45258</t>
+          <t>maa://41856</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>亚叶</t>
+          <t>早露</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C142" s="7" t="inlineStr">
@@ -10632,19 +10731,19 @@
       </c>
       <c r="D142" s="19" t="inlineStr">
         <is>
-          <t>maa://20981</t>
+          <t>maa://29025</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>断崖</t>
+          <t>卡达</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
@@ -10654,107 +10753,107 @@
       </c>
       <c r="D143" s="19" t="inlineStr">
         <is>
-          <t>maa://37689</t>
+          <t>maa://45258</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>亚叶</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>TW-7</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C144" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D144" s="19" t="inlineStr">
         <is>
-          <t>maa://28484, *maa://31185, *maa://30306</t>
+          <t>maa://20981</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>铃兰</t>
+          <t>断崖</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D145" s="19" t="inlineStr">
         <is>
-          <t>maa://30670, maa://31470, maa://61380</t>
+          <t>maa://37689</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>稀音</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>TW-7</t>
         </is>
       </c>
       <c r="C146" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D146" s="19" t="inlineStr">
         <is>
-          <t>maa://20971</t>
+          <t>maa://28484, *maa://31185, *maa://30306</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>蜜蜡</t>
+          <t>铃兰</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D147" s="19" t="inlineStr">
         <is>
-          <t>maa://39147</t>
+          <t>maa://30670, maa://31470, maa://61380</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
-          <t>贾维</t>
+          <t>稀音</t>
         </is>
       </c>
       <c r="B148" s="6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C148" s="7" t="inlineStr">
@@ -10764,19 +10863,19 @@
       </c>
       <c r="D148" s="19" t="inlineStr">
         <is>
-          <t>maa://20898</t>
+          <t>maa://20971</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="6" t="inlineStr">
         <is>
-          <t>孑</t>
+          <t>蜜蜡</t>
         </is>
       </c>
       <c r="B149" s="6" t="inlineStr">
         <is>
-          <t>S3-2</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
@@ -10786,63 +10885,63 @@
       </c>
       <c r="D149" s="19" t="inlineStr">
         <is>
-          <t>maa://29056</t>
+          <t>maa://39147</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
         <is>
-          <t>安哲拉</t>
+          <t>贾维</t>
         </is>
       </c>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="C150" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D150" s="19" t="inlineStr">
         <is>
-          <t>maa://28828, maa://20846</t>
+          <t>maa://20898</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="6" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>孑</t>
         </is>
       </c>
       <c r="B151" s="6" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>S3-2</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D151" s="19" t="inlineStr">
         <is>
-          <t>maa://40957, maa://36641, maa://36865, maa://44635, maa://44660, *maa://41128, maa://46108, maa://42918, maa://44119, *maa://64408, *maa://37300</t>
+          <t>maa://29056</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
         <is>
-          <t>棘刺</t>
+          <t>安哲拉</t>
         </is>
       </c>
       <c r="B152" s="6" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C152" s="7" t="inlineStr">
@@ -10852,63 +10951,63 @@
       </c>
       <c r="D152" s="19" t="inlineStr">
         <is>
-          <t>maa://51549, maa://51923</t>
+          <t>maa://28828, maa://20846</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="6" t="inlineStr">
         <is>
-          <t>酸糖</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B153" s="6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D153" s="19" t="inlineStr">
         <is>
-          <t>maa://20961</t>
+          <t>maa://40957, maa://36641, maa://36865, maa://44635, maa://44660, *maa://41128, maa://46108, maa://42918, maa://44119, *maa://64408, *maa://37300</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
         <is>
-          <t>特米米</t>
+          <t>棘刺</t>
         </is>
       </c>
       <c r="B154" s="6" t="inlineStr">
         <is>
-          <t>RI-2</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="C154" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D154" s="19" t="inlineStr">
         <is>
-          <t>maa://20963</t>
+          <t>maa://51549, maa://51923</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
         <is>
-          <t>燧石</t>
+          <t>酸糖</t>
         </is>
       </c>
       <c r="B155" s="6" t="inlineStr">
         <is>
-          <t>RI-9</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
@@ -10918,41 +11017,41 @@
       </c>
       <c r="D155" s="19" t="inlineStr">
         <is>
-          <t>maa://39148</t>
+          <t>maa://20961</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>特米米</t>
         </is>
       </c>
       <c r="B156" s="6" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>RI-2</t>
         </is>
       </c>
       <c r="C156" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D156" s="19" t="inlineStr">
         <is>
-          <t>maa://20946, maa://20833</t>
+          <t>maa://20963</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="6" t="inlineStr">
         <is>
-          <t>森蚺</t>
+          <t>燧石</t>
         </is>
       </c>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>RI-9</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
@@ -10962,41 +11061,41 @@
       </c>
       <c r="D157" s="19" t="inlineStr">
         <is>
-          <t>maa://20945</t>
+          <t>maa://39148</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
         <is>
-          <t>芳汀</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C158" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D158" s="19" t="inlineStr">
         <is>
-          <t>maa://37694</t>
+          <t>maa://20946, maa://20833</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="6" t="inlineStr">
         <is>
-          <t>薄绿</t>
+          <t>森蚺</t>
         </is>
       </c>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
@@ -11006,19 +11105,19 @@
       </c>
       <c r="D159" s="19" t="inlineStr">
         <is>
-          <t>maa://39149</t>
+          <t>maa://20945</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
         <is>
-          <t>四月</t>
+          <t>芳汀</t>
         </is>
       </c>
       <c r="B160" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="C160" s="7" t="inlineStr">
@@ -11028,41 +11127,41 @@
       </c>
       <c r="D160" s="19" t="inlineStr">
         <is>
-          <t>maa://20959</t>
+          <t>maa://37694</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="6" t="inlineStr">
         <is>
-          <t>史尔特尔</t>
+          <t>薄绿</t>
         </is>
       </c>
       <c r="B161" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D161" s="19" t="inlineStr">
         <is>
-          <t>maa://44232, *maa://45603</t>
+          <t>maa://39149</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
         <is>
-          <t>泡泡</t>
+          <t>四月</t>
         </is>
       </c>
       <c r="B162" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C162" s="7" t="inlineStr">
@@ -11072,41 +11171,41 @@
       </c>
       <c r="D162" s="19" t="inlineStr">
         <is>
-          <t>maa://20936</t>
+          <t>maa://20959</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="6" t="inlineStr">
         <is>
-          <t>鞭刃</t>
+          <t>史尔特尔</t>
         </is>
       </c>
       <c r="B163" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>maa://20855</t>
+          <t>maa://44232, *maa://45603</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
         <is>
-          <t>奥斯塔</t>
+          <t>泡泡</t>
         </is>
       </c>
       <c r="B164" s="6" t="inlineStr">
         <is>
-          <t>6-8</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C164" s="7" t="inlineStr">
@@ -11116,41 +11215,41 @@
       </c>
       <c r="D164" s="19" t="inlineStr">
         <is>
-          <t>maa://40158</t>
+          <t>maa://20936</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="6" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>鞭刃</t>
         </is>
       </c>
       <c r="B165" s="6" t="inlineStr">
         <is>
-          <t>MN-4</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D165" s="19" t="inlineStr">
         <is>
-          <t>*maa://32845, maa://29054</t>
+          <t>maa://20855</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
         <is>
-          <t>瑕光</t>
+          <t>奥斯塔</t>
         </is>
       </c>
       <c r="B166" s="6" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>6-8</t>
         </is>
       </c>
       <c r="C166" s="7" t="inlineStr">
@@ -11160,151 +11259,151 @@
       </c>
       <c r="D166" s="19" t="inlineStr">
         <is>
-          <t>maa://20973</t>
+          <t>maa://40158</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="6" t="inlineStr">
         <is>
-          <t>杰克</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B167" s="6" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>MN-4</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D167" s="19" t="inlineStr">
         <is>
-          <t>maa://39150</t>
+          <t>*maa://32845, maa://29054</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
         <is>
-          <t>絮雨</t>
+          <t>瑕光</t>
         </is>
       </c>
       <c r="B168" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C168" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D168" s="19" t="inlineStr">
         <is>
-          <t>maa://20975, maa://47950, maa://30806</t>
+          <t>maa://20973</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="6" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>杰克</t>
         </is>
       </c>
       <c r="B169" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D169" s="19" t="inlineStr">
         <is>
-          <t>maa://29633, maa://29627, *maa://29659, maa://49074, maa://29861, *maa://42343</t>
+          <t>maa://39150</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
         <is>
-          <t>泥岩</t>
+          <t>絮雨</t>
         </is>
       </c>
       <c r="B170" s="6" t="inlineStr">
         <is>
-          <t>10-16</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C170" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D170" s="19" t="inlineStr">
         <is>
-          <t>maa://49867, maa://49655</t>
+          <t>maa://20975, maa://47950, maa://30806</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
         <is>
-          <t>迷迭香</t>
+          <t>泥岩</t>
         </is>
       </c>
       <c r="B171" s="6" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D171" s="19" t="inlineStr">
         <is>
-          <t>maa://29059</t>
+          <t>maa://29633, maa://29627, *maa://29659, maa://49074, maa://29861, *maa://42343</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>泥岩</t>
         </is>
       </c>
       <c r="B172" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>10-16</t>
         </is>
       </c>
       <c r="C172" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D172" s="19" t="inlineStr">
         <is>
-          <t>maa://45556</t>
+          <t>maa://49867, maa://49655</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
         <is>
-          <t>松果</t>
+          <t>迷迭香</t>
         </is>
       </c>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
@@ -11314,19 +11413,19 @@
       </c>
       <c r="D173" s="19" t="inlineStr">
         <is>
-          <t>maa://40159</t>
+          <t>maa://29059</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
         <is>
-          <t>罗宾</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>BI-EX-2</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C174" s="7" t="inlineStr">
@@ -11336,19 +11435,19 @@
       </c>
       <c r="D174" s="19" t="inlineStr">
         <is>
-          <t>maa://39152</t>
+          <t>maa://45556</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
         <is>
-          <t>卡夫卡</t>
+          <t>松果</t>
         </is>
       </c>
       <c r="B175" s="6" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
@@ -11358,107 +11457,107 @@
       </c>
       <c r="D175" s="19" t="inlineStr">
         <is>
-          <t>maa://20905</t>
+          <t>maa://40159</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>罗宾</t>
         </is>
       </c>
       <c r="B176" s="6" t="inlineStr">
         <is>
-          <t>LE-5</t>
+          <t>BI-EX-2</t>
         </is>
       </c>
       <c r="C176" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D176" s="19" t="inlineStr">
         <is>
-          <t>maa://64200, maa://59681</t>
+          <t>maa://39152</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="6" t="inlineStr">
         <is>
-          <t>山</t>
+          <t>卡夫卡</t>
         </is>
       </c>
       <c r="B177" s="6" t="inlineStr">
         <is>
-          <t>MB-EX-3</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D177" s="19" t="inlineStr">
         <is>
-          <t>maa://32418, maa://63320, maa://51440</t>
+          <t>maa://20905</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
         <is>
-          <t>豆苗</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B178" s="6" t="inlineStr">
         <is>
-          <t>S3-7</t>
+          <t>LE-5</t>
         </is>
       </c>
       <c r="C178" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D178" s="19" t="inlineStr">
         <is>
-          <t>maa://37690</t>
+          <t>maa://64200, maa://59681</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="6" t="inlineStr">
         <is>
-          <t>爱丽丝</t>
+          <t>山</t>
         </is>
       </c>
       <c r="B179" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>MB-EX-3</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D179" s="19" t="inlineStr">
         <is>
-          <t>maa://20842</t>
+          <t>maa://32418, maa://63320, maa://51440</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>豆苗</t>
         </is>
       </c>
       <c r="B180" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>S3-7</t>
         </is>
       </c>
       <c r="C180" s="7" t="inlineStr">
@@ -11468,41 +11567,41 @@
       </c>
       <c r="D180" s="19" t="inlineStr">
         <is>
-          <t>maa://20912</t>
+          <t>maa://37690</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="6" t="inlineStr">
         <is>
-          <t>空弦</t>
+          <t>爱丽丝</t>
         </is>
       </c>
       <c r="B181" s="6" t="inlineStr">
         <is>
-          <t>2-9</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D181" s="19" t="inlineStr">
         <is>
-          <t>maa://20911, *maa://29012</t>
+          <t>maa://20842</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
         <is>
-          <t>图耶</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B182" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C182" s="7" t="inlineStr">
@@ -11512,41 +11611,41 @@
       </c>
       <c r="D182" s="19" t="inlineStr">
         <is>
-          <t>maa://20964</t>
+          <t>maa://20912</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="6" t="inlineStr">
         <is>
-          <t>炎狱炎熔</t>
+          <t>空弦</t>
         </is>
       </c>
       <c r="B183" s="6" t="inlineStr">
         <is>
-          <t>WR-4</t>
+          <t>2-9</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D183" s="19" t="inlineStr">
         <is>
-          <t>maa://20983</t>
+          <t>maa://20911, *maa://29012</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
         <is>
-          <t>乌有</t>
+          <t>图耶</t>
         </is>
       </c>
       <c r="B184" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C184" s="7" t="inlineStr">
@@ -11556,19 +11655,19 @@
       </c>
       <c r="D184" s="19" t="inlineStr">
         <is>
-          <t>maa://31560</t>
+          <t>maa://20964</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="6" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>炎狱炎熔</t>
         </is>
       </c>
       <c r="B185" s="6" t="inlineStr">
         <is>
-          <t>WR-3</t>
+          <t>WR-4</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
@@ -11578,19 +11677,19 @@
       </c>
       <c r="D185" s="19" t="inlineStr">
         <is>
-          <t>maa://28104</t>
+          <t>maa://20983</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
         <is>
-          <t>嵯峨</t>
+          <t>乌有</t>
         </is>
       </c>
       <c r="B186" s="6" t="inlineStr">
         <is>
-          <t>WR-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C186" s="7" t="inlineStr">
@@ -11600,19 +11699,19 @@
       </c>
       <c r="D186" s="19" t="inlineStr">
         <is>
-          <t>maa://20861</t>
+          <t>maa://31560</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="6" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B187" s="6" t="inlineStr">
         <is>
-          <t>1-6</t>
+          <t>WR-3</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
@@ -11622,41 +11721,41 @@
       </c>
       <c r="D187" s="19" t="inlineStr">
         <is>
-          <t>maa://20970</t>
+          <t>maa://28104</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
         <is>
-          <t>夕</t>
+          <t>嵯峨</t>
         </is>
       </c>
       <c r="B188" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>WR-1</t>
         </is>
       </c>
       <c r="C188" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D188" s="19" t="inlineStr">
         <is>
-          <t>maa://20969, maa://41303</t>
+          <t>maa://20861</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="6" t="inlineStr">
         <is>
-          <t>战车</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B189" s="6" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>1-6</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
@@ -11666,41 +11765,41 @@
       </c>
       <c r="D189" s="19" t="inlineStr">
         <is>
-          <t>maa://20999</t>
+          <t>maa://20970</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
         <is>
-          <t>闪击</t>
+          <t>夕</t>
         </is>
       </c>
       <c r="B190" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C190" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D190" s="19" t="inlineStr">
         <is>
-          <t>maa://35198</t>
+          <t>maa://20969, maa://41303</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="6" t="inlineStr">
         <is>
-          <t>霜华</t>
+          <t>战车</t>
         </is>
       </c>
       <c r="B191" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
@@ -11710,107 +11809,107 @@
       </c>
       <c r="D191" s="19" t="inlineStr">
         <is>
-          <t>maa://39153</t>
+          <t>maa://20999</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>闪击</t>
         </is>
       </c>
       <c r="B192" s="6" t="inlineStr">
         <is>
-          <t>SV-8</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C192" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D192" s="19" t="inlineStr">
         <is>
-          <t>maa://34866, maa://34714</t>
+          <t>maa://35198</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="6" t="inlineStr">
         <is>
-          <t>灰烬</t>
+          <t>霜华</t>
         </is>
       </c>
       <c r="B193" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D193" s="19" t="inlineStr">
         <is>
-          <t>maa://34883, maa://20895</t>
+          <t>maa://39153</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>暴雨</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>SV-8</t>
         </is>
       </c>
       <c r="C194" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D194" s="19" t="inlineStr">
         <is>
-          <t>maa://20853</t>
+          <t>maa://34866, maa://34714</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="6" t="inlineStr">
         <is>
-          <t>熔泉</t>
+          <t>灰烬</t>
         </is>
       </c>
       <c r="B195" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D195" s="19" t="inlineStr">
         <is>
-          <t>maa://20942</t>
+          <t>maa://34883, maa://20895</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>暴雨</t>
         </is>
       </c>
       <c r="B196" s="6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="C196" s="7" t="inlineStr">
@@ -11820,41 +11919,41 @@
       </c>
       <c r="D196" s="19" t="inlineStr">
         <is>
-          <t>maa://20992</t>
+          <t>maa://20853</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
         <is>
-          <t>异客</t>
+          <t>熔泉</t>
         </is>
       </c>
       <c r="B197" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D197" s="19" t="inlineStr">
         <is>
-          <t>*maa://28190, maa://20994</t>
+          <t>maa://20942</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
         <is>
-          <t>赤冬</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B198" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="C198" s="7" t="inlineStr">
@@ -11864,107 +11963,107 @@
       </c>
       <c r="D198" s="19" t="inlineStr">
         <is>
-          <t>maa://20860</t>
+          <t>maa://20992</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="6" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>异客</t>
         </is>
       </c>
       <c r="B199" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D199" s="19" t="inlineStr">
         <is>
-          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://51066, maa://63024, *maa://70161</t>
+          <t>*maa://28190, maa://20994</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
         <is>
-          <t>歌蕾蒂娅</t>
+          <t>赤冬</t>
         </is>
       </c>
       <c r="B200" s="6" t="inlineStr">
         <is>
-          <t>SN-EX-3</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C200" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D200" s="19" t="inlineStr">
         <is>
-          <t>maa://39156, *maa://53417, *maa://63806</t>
+          <t>maa://20860</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="6" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B201" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SV-EX-5</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D201" s="19" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>maa://44224, maa://35854, maa://50388, maa://25760, *maa://51066, maa://63024, *maa://70161</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
         <is>
-          <t>凯尔希</t>
+          <t>歌蕾蒂娅</t>
         </is>
       </c>
       <c r="B202" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>SN-EX-3</t>
         </is>
       </c>
       <c r="C202" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D202" s="19" t="inlineStr">
         <is>
-          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
+          <t>maa://39156, *maa://53417, *maa://63806</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="6" t="inlineStr">
         <is>
-          <t>浊心斯卡蒂</t>
+          <t>凯尔希</t>
         </is>
       </c>
       <c r="B203" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
@@ -11974,63 +12073,63 @@
       </c>
       <c r="D203" s="19" t="inlineStr">
         <is>
-          <t>maa://42223, maa://49077, maa://42292, *maa://42402</t>
+          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
         <is>
-          <t>深靛</t>
+          <t>凯尔希</t>
         </is>
       </c>
       <c r="B204" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C204" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D204" s="19" t="inlineStr">
         <is>
-          <t>maa://39154</t>
+          <t>maa://27823, *maa://28190, maa://22894, *maa://20906</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="6" t="inlineStr">
         <is>
-          <t>贝娜</t>
+          <t>浊心斯卡蒂</t>
         </is>
       </c>
       <c r="B205" s="6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D205" s="19" t="inlineStr">
         <is>
-          <t>maa://20854</t>
+          <t>maa://42223, maa://49077, maa://42292, *maa://42402</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
         <is>
-          <t>绮良</t>
+          <t>深靛</t>
         </is>
       </c>
       <c r="B206" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C206" s="7" t="inlineStr">
@@ -12040,19 +12139,19 @@
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>maa://20937</t>
+          <t>maa://39154</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="6" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>贝娜</t>
         </is>
       </c>
       <c r="B207" s="6" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
@@ -12062,195 +12161,195 @@
       </c>
       <c r="D207" s="19" t="inlineStr">
         <is>
-          <t>maa://22468</t>
+          <t>maa://20854</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
         <is>
-          <t>卡涅利安</t>
+          <t>绮良</t>
         </is>
       </c>
       <c r="B208" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C208" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D208" s="19" t="inlineStr">
         <is>
-          <t>maa://30673, maa://30672</t>
+          <t>maa://20937</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="6" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B209" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D209" s="19" t="inlineStr">
         <is>
-          <t>maa://20934, maa://20827, maa://20828</t>
+          <t>maa://22468</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
         <is>
-          <t>帕拉斯</t>
+          <t>卡涅利安</t>
         </is>
       </c>
       <c r="B210" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C210" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D210" s="19" t="inlineStr">
         <is>
-          <t>maa://20935</t>
+          <t>maa://30673, maa://30672</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="6" t="inlineStr">
         <is>
-          <t>龙舌兰</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B211" s="6" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D211" s="19" t="inlineStr">
         <is>
-          <t>maa://53354</t>
+          <t>maa://20934, maa://20827, maa://20828</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
         <is>
-          <t>羽毛笔</t>
+          <t>帕拉斯</t>
         </is>
       </c>
       <c r="B212" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D212" s="19" t="inlineStr">
         <is>
-          <t>maa://28133, maa://25369</t>
+          <t>maa://20935</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="6" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>龙舌兰</t>
         </is>
       </c>
       <c r="B213" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D213" s="19" t="inlineStr">
         <is>
-          <t>maa://20956, *maa://20830, *maa://44703</t>
+          <t>maa://53354</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
         <is>
-          <t>水月</t>
+          <t>羽毛笔</t>
         </is>
       </c>
       <c r="B214" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C214" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D214" s="19" t="inlineStr">
         <is>
-          <t>maa://20955</t>
+          <t>maa://28133, maa://25369</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="6" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B215" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D215" s="19" t="inlineStr">
         <is>
-          <t>maa://39238</t>
+          <t>maa://20956, *maa://20830, *maa://44703</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
         <is>
-          <t>假日威龙陈</t>
+          <t>水月</t>
         </is>
       </c>
       <c r="B216" s="6" t="inlineStr">
         <is>
-          <t>DH-7</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C216" s="7" t="inlineStr">
@@ -12260,19 +12359,19 @@
       </c>
       <c r="D216" s="19" t="inlineStr">
         <is>
-          <t>maa://64044</t>
+          <t>maa://20955</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="6" t="inlineStr">
         <is>
-          <t>罗比菈塔</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B217" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
@@ -12282,19 +12381,19 @@
       </c>
       <c r="D217" s="19" t="inlineStr">
         <is>
-          <t>maa://45261</t>
+          <t>maa://39238</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
         <is>
-          <t>桑葚</t>
+          <t>假日威龙陈</t>
         </is>
       </c>
       <c r="B218" s="6" t="inlineStr">
         <is>
-          <t>SV-5</t>
+          <t>DH-7</t>
         </is>
       </c>
       <c r="C218" s="7" t="inlineStr">
@@ -12304,41 +12403,41 @@
       </c>
       <c r="D218" s="19" t="inlineStr">
         <is>
-          <t>maa://39694</t>
+          <t>maa://64044</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>罗比菈塔</t>
         </is>
       </c>
       <c r="B219" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D219" s="19" t="inlineStr">
         <is>
-          <t>maa://24636, maa://25778</t>
+          <t>maa://45261</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
         <is>
-          <t>琴柳</t>
+          <t>桑葚</t>
         </is>
       </c>
       <c r="B220" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>SV-5</t>
         </is>
       </c>
       <c r="C220" s="7" t="inlineStr">
@@ -12348,63 +12447,63 @@
       </c>
       <c r="D220" s="19" t="inlineStr">
         <is>
-          <t>maa://48261</t>
+          <t>maa://39694</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>灰毫</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B221" s="6" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D221" s="19" t="inlineStr">
         <is>
-          <t>maa://39157</t>
+          <t>maa://24636, maa://25778</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>琴柳</t>
         </is>
       </c>
       <c r="B222" s="6" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C222" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D222" s="19" t="inlineStr">
         <is>
-          <t>*maa://26496, maa://20995</t>
+          <t>maa://48261</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>远牙</t>
+          <t>灰毫</t>
         </is>
       </c>
       <c r="B223" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
@@ -12414,41 +12513,41 @@
       </c>
       <c r="D223" s="19" t="inlineStr">
         <is>
-          <t>maa://26499</t>
+          <t>maa://39157</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
         <is>
-          <t>布丁</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B224" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C224" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D224" s="19" t="inlineStr">
         <is>
-          <t>maa://20858</t>
+          <t>*maa://26496, maa://20995</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>蜜莓</t>
+          <t>远牙</t>
         </is>
       </c>
       <c r="B225" s="6" t="inlineStr">
         <is>
-          <t>GA-2</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C225" s="7" t="inlineStr">
@@ -12458,19 +12557,19 @@
       </c>
       <c r="D225" s="19" t="inlineStr">
         <is>
-          <t>maa://39695</t>
+          <t>maa://26499</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
         <is>
-          <t>野鬃</t>
+          <t>布丁</t>
         </is>
       </c>
       <c r="B226" s="6" t="inlineStr">
         <is>
-          <t>MN-2</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C226" s="7" t="inlineStr">
@@ -12480,19 +12579,19 @@
       </c>
       <c r="D226" s="19" t="inlineStr">
         <is>
-          <t>maa://20988</t>
+          <t>maa://20858</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>蚀清</t>
+          <t>蜜莓</t>
         </is>
       </c>
       <c r="B227" s="6" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>GA-2</t>
         </is>
       </c>
       <c r="C227" s="7" t="inlineStr">
@@ -12502,41 +12601,41 @@
       </c>
       <c r="D227" s="19" t="inlineStr">
         <is>
-          <t>maa://39158</t>
+          <t>maa://39695</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>野鬃</t>
         </is>
       </c>
       <c r="B228" s="6" t="inlineStr">
         <is>
-          <t>NL-5</t>
+          <t>MN-2</t>
         </is>
       </c>
       <c r="C228" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D228" s="19" t="inlineStr">
         <is>
-          <t>maa://28187, *maa://39520</t>
+          <t>maa://20988</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>焰尾</t>
+          <t>蚀清</t>
         </is>
       </c>
       <c r="B229" s="6" t="inlineStr">
         <is>
-          <t>NL-3</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C229" s="7" t="inlineStr">
@@ -12546,19 +12645,19 @@
       </c>
       <c r="D229" s="19" t="inlineStr">
         <is>
-          <t>maa://20985</t>
+          <t>maa://39158</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B230" s="6" t="inlineStr">
         <is>
-          <t>MN-8</t>
+          <t>NL-5</t>
         </is>
       </c>
       <c r="C230" s="7" t="inlineStr">
@@ -12568,80 +12667,80 @@
       </c>
       <c r="D230" s="19" t="inlineStr">
         <is>
-          <t>maa://20987, *maa://35801</t>
+          <t>maa://28187, *maa://39520</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>耀骑士临光</t>
+          <t>焰尾</t>
         </is>
       </c>
       <c r="B231" s="6" t="inlineStr">
         <is>
-          <t>NL-10</t>
+          <t>NL-3</t>
         </is>
       </c>
       <c r="C231" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D231" s="19" t="inlineStr">
         <is>
-          <t>*maa://29644, maa://39159</t>
+          <t>maa://20985</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
         <is>
-          <t>耶拉</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B232" s="6" t="inlineStr">
         <is>
-          <t>BI-7</t>
+          <t>MN-8</t>
         </is>
       </c>
       <c r="C232" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D232" s="19" t="inlineStr">
         <is>
-          <t>maa://30677</t>
+          <t>maa://20987, *maa://35801</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>极光</t>
+          <t>耀骑士临光</t>
         </is>
       </c>
       <c r="B233" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>NL-10</t>
         </is>
       </c>
       <c r="C233" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D233" s="19" t="inlineStr">
         <is>
-          <t>maa://20896</t>
+          <t>*maa://29644, maa://39159</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>耶拉</t>
         </is>
       </c>
       <c r="B234" s="6" t="inlineStr">
@@ -12651,24 +12750,24 @@
       </c>
       <c r="C234" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D234" s="19" t="inlineStr">
         <is>
-          <t>maa://29058, maa://39140, *maa://38723</t>
+          <t>maa://30677</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>灵知</t>
+          <t>极光</t>
         </is>
       </c>
       <c r="B235" s="6" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C235" s="7" t="inlineStr">
@@ -12678,41 +12777,41 @@
       </c>
       <c r="D235" s="19" t="inlineStr">
         <is>
-          <t>maa://48263</t>
+          <t>maa://20896</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
         <is>
-          <t>九色鹿</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B236" s="6" t="inlineStr">
         <is>
-          <t>IW-3</t>
+          <t>BI-7</t>
         </is>
       </c>
       <c r="C236" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D236" s="19" t="inlineStr">
         <is>
-          <t>maa://39160</t>
+          <t>maa://29058, maa://39140, *maa://38723</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>寒芒克洛丝</t>
+          <t>灵知</t>
         </is>
       </c>
       <c r="B237" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C237" s="7" t="inlineStr">
@@ -12722,41 +12821,41 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>maa://49491</t>
+          <t>maa://48263</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
         <is>
-          <t>夜半</t>
+          <t>暮落</t>
         </is>
       </c>
       <c r="B238" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C238" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D238" s="19" t="inlineStr">
         <is>
-          <t>maa://35952</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="6" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>九色鹿</t>
         </is>
       </c>
       <c r="B239" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>IW-3</t>
         </is>
       </c>
       <c r="C239" s="7" t="inlineStr">
@@ -12766,63 +12865,63 @@
       </c>
       <c r="D239" s="19" t="inlineStr">
         <is>
-          <t>maa://20917</t>
+          <t>maa://39160</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
         <is>
-          <t>老鲤</t>
+          <t>寒芒克洛丝</t>
         </is>
       </c>
       <c r="B240" s="6" t="inlineStr">
         <is>
-          <t>IW-EX-1</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C240" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D240" s="19" t="inlineStr">
         <is>
-          <t>maa://30714, maa://30675</t>
+          <t>maa://49491</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="6" t="inlineStr">
         <is>
-          <t>令</t>
+          <t>夜半</t>
         </is>
       </c>
       <c r="B241" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C241" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D241" s="19" t="inlineStr">
         <is>
-          <t>maa://20922, *maa://32623, *maa://34242</t>
+          <t>maa://35952</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
         <is>
-          <t>夏栎</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B242" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C242" s="7" t="inlineStr">
@@ -12832,63 +12931,63 @@
       </c>
       <c r="D242" s="19" t="inlineStr">
         <is>
-          <t>maa://32999</t>
+          <t>maa://20917</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="6" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>老鲤</t>
         </is>
       </c>
       <c r="B243" s="6" t="inlineStr">
         <is>
-          <t>R8-8</t>
+          <t>IW-EX-1</t>
         </is>
       </c>
       <c r="C243" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D243" s="19" t="inlineStr">
         <is>
-          <t>maa://30667, maa://30666, *maa://30723, maa://39588, *maa://64079, *maa://65726, *maa://68226</t>
+          <t>maa://30714, maa://30675</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
         <is>
-          <t>澄闪</t>
+          <t>令</t>
         </is>
       </c>
       <c r="B244" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C244" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>maa://62759, *maa://70680</t>
+          <t>maa://20922, *maa://32623, *maa://34242</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="6" t="inlineStr">
         <is>
-          <t>见行者</t>
+          <t>夏栎</t>
         </is>
       </c>
       <c r="B245" s="6" t="inlineStr">
         <is>
-          <t>GA-EX-1</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C245" s="7" t="inlineStr">
@@ -12898,85 +12997,85 @@
       </c>
       <c r="D245" s="19" t="inlineStr">
         <is>
-          <t>maa://30512</t>
+          <t>maa://32999</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
         <is>
-          <t>风丸</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B246" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>R8-8</t>
         </is>
       </c>
       <c r="C246" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D246" s="19" t="inlineStr">
         <is>
-          <t>maa://20870</t>
+          <t>maa://30667, maa://30666, *maa://30723, maa://39588, *maa://64079, *maa://65726, *maa://68226</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="6" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>澄闪</t>
         </is>
       </c>
       <c r="B247" s="6" t="inlineStr">
         <is>
-          <t>GA-4</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C247" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D247" s="19" t="inlineStr">
         <is>
-          <t>maa://29024</t>
+          <t>maa://62759, *maa://70680</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
         <is>
-          <t>菲亚梅塔</t>
+          <t>见行者</t>
         </is>
       </c>
       <c r="B248" s="6" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>GA-EX-1</t>
         </is>
       </c>
       <c r="C248" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D248" s="19" t="inlineStr">
         <is>
-          <t>maa://20867, maa://38485</t>
+          <t>maa://30512</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="6" t="inlineStr">
         <is>
-          <t>褐果</t>
+          <t>风丸</t>
         </is>
       </c>
       <c r="B249" s="6" t="inlineStr">
         <is>
-          <t>SV-3</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C249" s="7" t="inlineStr">
@@ -12986,19 +13085,19 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>maa://40160</t>
+          <t>maa://20870</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
         <is>
-          <t>海蒂</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B250" s="6" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>GA-4</t>
         </is>
       </c>
       <c r="C250" s="7" t="inlineStr">
@@ -13008,85 +13107,85 @@
       </c>
       <c r="D250" s="19" t="inlineStr">
         <is>
-          <t>maa://43089</t>
+          <t>maa://29024</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="6" t="inlineStr">
         <is>
-          <t>洛洛</t>
+          <t>菲亚梅塔</t>
         </is>
       </c>
       <c r="B251" s="6" t="inlineStr">
         <is>
-          <t>RI-EX-4</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D251" s="19" t="inlineStr">
         <is>
-          <t>maa://30674</t>
+          <t>maa://20867, maa://38485</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>褐果</t>
         </is>
       </c>
       <c r="B252" s="6" t="inlineStr">
         <is>
-          <t>7-15</t>
+          <t>SV-3</t>
         </is>
       </c>
       <c r="C252" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D252" s="19" t="inlineStr">
         <is>
-          <t>maa://28923, maa://28906, *maa://65613</t>
+          <t>maa://40160</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="6" t="inlineStr">
         <is>
-          <t>号角</t>
+          <t>海蒂</t>
         </is>
       </c>
       <c r="B253" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C253" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D253" s="19" t="inlineStr">
         <is>
-          <t>maa://42287, maa://45570, maa://60678, maa://42225</t>
+          <t>maa://43089</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
         <is>
-          <t>掠风</t>
+          <t>洛洛</t>
         </is>
       </c>
       <c r="B254" s="6" t="inlineStr">
         <is>
-          <t>11-9</t>
+          <t>RI-EX-4</t>
         </is>
       </c>
       <c r="C254" s="7" t="inlineStr">
@@ -13096,85 +13195,85 @@
       </c>
       <c r="D254" s="19" t="inlineStr">
         <is>
-          <t>maa://39161</t>
+          <t>maa://30674</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="6" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B255" s="6" t="inlineStr">
         <is>
-          <t>6-9</t>
+          <t>7-15</t>
         </is>
       </c>
       <c r="C255" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D255" s="19" t="inlineStr">
         <is>
-          <t>maa://20923</t>
+          <t>maa://28923, maa://28906, *maa://65613</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
         <is>
-          <t>流明</t>
+          <t>号角</t>
         </is>
       </c>
       <c r="B256" s="6" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C256" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D256" s="19" t="inlineStr">
         <is>
-          <t>maa://31559, maa://24093, maa://20924</t>
+          <t>maa://42287, maa://45570, maa://60678, maa://42225</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="6" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>掠风</t>
         </is>
       </c>
       <c r="B257" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>11-9</t>
         </is>
       </c>
       <c r="C257" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D257" s="19" t="inlineStr">
         <is>
-          <t>maa://40958, *maa://45067</t>
+          <t>maa://39161</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
         <is>
-          <t>艾丽妮</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B258" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>6-9</t>
         </is>
       </c>
       <c r="C258" s="7" t="inlineStr">
@@ -13184,41 +13283,41 @@
       </c>
       <c r="D258" s="19" t="inlineStr">
         <is>
-          <t>maa://20840</t>
+          <t>maa://20923</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="6" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>流明</t>
         </is>
       </c>
       <c r="B259" s="6" t="inlineStr">
         <is>
-          <t>SV-EX-1</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C259" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D259" s="19" t="inlineStr">
         <is>
-          <t>maa://20877, *maa://20836</t>
+          <t>maa://31559, maa://24093, maa://20924</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
         <is>
-          <t>归溟幽灵鲨</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B260" s="6" t="inlineStr">
         <is>
-          <t>S4-1</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C260" s="7" t="inlineStr">
@@ -13228,19 +13327,19 @@
       </c>
       <c r="D260" s="19" t="inlineStr">
         <is>
-          <t>maa://20879, maa://20834</t>
+          <t>maa://40958, *maa://45067</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="6" t="inlineStr">
         <is>
-          <t>埃拉托</t>
+          <t>艾丽妮</t>
         </is>
       </c>
       <c r="B261" s="6" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C261" s="7" t="inlineStr">
@@ -13250,41 +13349,41 @@
       </c>
       <c r="D261" s="19" t="inlineStr">
         <is>
-          <t>maa://20839</t>
+          <t>maa://20840</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
         <is>
-          <t>濯尘芙蓉</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B262" s="6" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>SV-EX-1</t>
         </is>
       </c>
       <c r="C262" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D262" s="19" t="inlineStr">
         <is>
-          <t>maa://30676</t>
+          <t>maa://20877, *maa://20836</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>归溟幽灵鲨</t>
         </is>
       </c>
       <c r="B263" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>S4-1</t>
         </is>
       </c>
       <c r="C263" s="7" t="inlineStr">
@@ -13294,19 +13393,19 @@
       </c>
       <c r="D263" s="19" t="inlineStr">
         <is>
-          <t>maa://31560, maa://20884</t>
+          <t>maa://20879, maa://20834</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>埃拉托</t>
         </is>
       </c>
       <c r="B264" s="6" t="inlineStr">
         <is>
-          <t>3-6</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C264" s="7" t="inlineStr">
@@ -13316,41 +13415,41 @@
       </c>
       <c r="D264" s="19" t="inlineStr">
         <is>
-          <t>maa://47204</t>
+          <t>maa://20839</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="6" t="inlineStr">
         <is>
-          <t>黑键</t>
+          <t>车尔尼</t>
         </is>
       </c>
       <c r="B265" s="6" t="inlineStr">
         <is>
-          <t>11-12</t>
+          <t>LE-3</t>
         </is>
       </c>
       <c r="C265" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D265" s="19" t="inlineStr">
         <is>
-          <t>maa://29027</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="6" t="inlineStr">
         <is>
-          <t>星源</t>
+          <t>濯尘芙蓉</t>
         </is>
       </c>
       <c r="B266" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C266" s="7" t="inlineStr">
@@ -13360,41 +13459,41 @@
       </c>
       <c r="D266" s="19" t="inlineStr">
         <is>
-          <t>maa://20977</t>
+          <t>maa://30676</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="6" t="inlineStr">
         <is>
-          <t>承曦格雷伊</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B267" s="6" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C267" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D267" s="19" t="inlineStr">
         <is>
-          <t>maa://39162</t>
+          <t>maa://31560, maa://20884</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="6" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B268" s="6" t="inlineStr">
         <is>
-          <t>MB-EX-1</t>
+          <t>3-6</t>
         </is>
       </c>
       <c r="C268" s="7" t="inlineStr">
@@ -13404,19 +13503,19 @@
       </c>
       <c r="D268" s="19" t="inlineStr">
         <is>
-          <t>maa://59682</t>
+          <t>maa://47204</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="6" t="inlineStr">
         <is>
-          <t>多萝西</t>
+          <t>黑键</t>
         </is>
       </c>
       <c r="B269" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>11-12</t>
         </is>
       </c>
       <c r="C269" s="7" t="inlineStr">
@@ -13426,19 +13525,19 @@
       </c>
       <c r="D269" s="19" t="inlineStr">
         <is>
-          <t>maa://22467</t>
+          <t>maa://29027</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="6" t="inlineStr">
         <is>
-          <t>至简</t>
+          <t>星源</t>
         </is>
       </c>
       <c r="B270" s="6" t="inlineStr">
         <is>
-          <t>IC-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C270" s="7" t="inlineStr">
@@ -13448,19 +13547,19 @@
       </c>
       <c r="D270" s="19" t="inlineStr">
         <is>
-          <t>maa://59689</t>
+          <t>maa://20977</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="6" t="inlineStr">
         <is>
-          <t>晓歌</t>
+          <t>承曦格雷伊</t>
         </is>
       </c>
       <c r="B271" s="6" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="C271" s="7" t="inlineStr">
@@ -13470,19 +13569,19 @@
       </c>
       <c r="D271" s="19" t="inlineStr">
         <is>
-          <t>maa://49643</t>
+          <t>maa://39162</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="6" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>多萝西</t>
         </is>
       </c>
       <c r="B272" s="6" t="inlineStr">
         <is>
-          <t>9-7</t>
+          <t>MB-EX-1</t>
         </is>
       </c>
       <c r="C272" s="7" t="inlineStr">
@@ -13492,41 +13591,41 @@
       </c>
       <c r="D272" s="19" t="inlineStr">
         <is>
-          <t>maa://48265</t>
+          <t>maa://59682</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="6" t="inlineStr">
         <is>
-          <t>鸿雪</t>
+          <t>多萝西</t>
         </is>
       </c>
       <c r="B273" s="6" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C273" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D273" s="19" t="inlineStr">
         <is>
-          <t>maa://20825, maa://21445, *maa://35726</t>
+          <t>maa://22467</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="6" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>至简</t>
         </is>
       </c>
       <c r="B274" s="6" t="inlineStr">
         <is>
-          <t>9-2</t>
+          <t>IC-8</t>
         </is>
       </c>
       <c r="C274" s="7" t="inlineStr">
@@ -13536,19 +13635,19 @@
       </c>
       <c r="D274" s="19" t="inlineStr">
         <is>
-          <t>maa://25769</t>
+          <t>maa://59689</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="6" t="inlineStr">
         <is>
-          <t>百炼嘉维尔</t>
+          <t>晓歌</t>
         </is>
       </c>
       <c r="B275" s="6" t="inlineStr">
         <is>
-          <t>RI-9</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="C275" s="7" t="inlineStr">
@@ -13558,19 +13657,19 @@
       </c>
       <c r="D275" s="19" t="inlineStr">
         <is>
-          <t>maa://67819</t>
+          <t>maa://49643</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="6" t="inlineStr">
         <is>
-          <t>但书</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B276" s="6" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>9-7</t>
         </is>
       </c>
       <c r="C276" s="7" t="inlineStr">
@@ -13580,41 +13679,41 @@
       </c>
       <c r="D276" s="19" t="inlineStr">
         <is>
-          <t>maa://20862</t>
+          <t>maa://48265</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="6" t="inlineStr">
         <is>
-          <t>玛恩纳</t>
+          <t>鸿雪</t>
         </is>
       </c>
       <c r="B277" s="6" t="inlineStr">
         <is>
-          <t>11-15</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="C277" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D277" s="19" t="inlineStr">
         <is>
-          <t>maa://51881, maa://51630, maa://56588, *maa://51893, *maa://66758</t>
+          <t>maa://20825, maa://21445, *maa://35726</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="6" t="inlineStr">
         <is>
-          <t>罗小黑</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B278" s="6" t="inlineStr">
         <is>
-          <t>IW-4</t>
+          <t>9-2</t>
         </is>
       </c>
       <c r="C278" s="7" t="inlineStr">
@@ -13624,19 +13723,19 @@
       </c>
       <c r="D278" s="19" t="inlineStr">
         <is>
-          <t>maa://39163</t>
+          <t>maa://25769</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="6" t="inlineStr">
         <is>
-          <t>海沫</t>
+          <t>百炼嘉维尔</t>
         </is>
       </c>
       <c r="B279" s="6" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>RI-9</t>
         </is>
       </c>
       <c r="C279" s="7" t="inlineStr">
@@ -13646,19 +13745,19 @@
       </c>
       <c r="D279" s="19" t="inlineStr">
         <is>
-          <t>maa://29061</t>
+          <t>maa://67819</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="6" t="inlineStr">
         <is>
-          <t>铅踝</t>
+          <t>但书</t>
         </is>
       </c>
       <c r="B280" s="6" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="C280" s="7" t="inlineStr">
@@ -13668,63 +13767,63 @@
       </c>
       <c r="D280" s="19" t="inlineStr">
         <is>
-          <t>maa://20939</t>
+          <t>maa://20862</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="6" t="inlineStr">
         <is>
-          <t>达格达</t>
+          <t>玛恩纳</t>
         </is>
       </c>
       <c r="B281" s="6" t="inlineStr">
         <is>
-          <t>11-5</t>
+          <t>11-15</t>
         </is>
       </c>
       <c r="C281" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D281" s="19" t="inlineStr">
         <is>
-          <t>maa://39164</t>
+          <t>maa://51881, maa://51630, maa://56588, *maa://51893, *maa://66758</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="6" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>罗小黑</t>
         </is>
       </c>
       <c r="B282" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>IW-4</t>
         </is>
       </c>
       <c r="C282" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D282" s="19" t="inlineStr">
         <is>
-          <t>maa://28133, maa://33394</t>
+          <t>maa://39163</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="6" t="inlineStr">
         <is>
-          <t>白铁</t>
+          <t>海沫</t>
         </is>
       </c>
       <c r="B283" s="6" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C283" s="7" t="inlineStr">
@@ -13734,19 +13833,19 @@
       </c>
       <c r="D283" s="19" t="inlineStr">
         <is>
-          <t>maa://42311</t>
+          <t>maa://29061</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="6" t="inlineStr">
         <is>
-          <t>石英</t>
+          <t>铅踝</t>
         </is>
       </c>
       <c r="B284" s="6" t="inlineStr">
         <is>
-          <t>DH-4</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C284" s="7" t="inlineStr">
@@ -13756,19 +13855,19 @@
       </c>
       <c r="D284" s="19" t="inlineStr">
         <is>
-          <t>maa://41362</t>
+          <t>maa://20939</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="6" t="inlineStr">
         <is>
-          <t>雪绒</t>
+          <t>达格达</t>
         </is>
       </c>
       <c r="B285" s="6" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>11-5</t>
         </is>
       </c>
       <c r="C285" s="7" t="inlineStr">
@@ -13778,41 +13877,41 @@
       </c>
       <c r="D285" s="19" t="inlineStr">
         <is>
-          <t>maa://20978</t>
+          <t>maa://39164</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="6" t="inlineStr">
         <is>
-          <t>子月</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B286" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C286" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D286" s="19" t="inlineStr">
         <is>
-          <t>maa://21002</t>
+          <t>maa://28133, maa://33394</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="6" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>白铁</t>
         </is>
       </c>
       <c r="B287" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C287" s="7" t="inlineStr">
@@ -13822,41 +13921,41 @@
       </c>
       <c r="D287" s="19" t="inlineStr">
         <is>
-          <t>maa://39165</t>
+          <t>maa://42311</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="6" t="inlineStr">
         <is>
-          <t>伺夜</t>
+          <t>石英</t>
         </is>
       </c>
       <c r="B288" s="6" t="inlineStr">
         <is>
-          <t>IS-6</t>
+          <t>DH-4</t>
         </is>
       </c>
       <c r="C288" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D288" s="19" t="inlineStr">
         <is>
-          <t>maa://48267, maa://48266</t>
+          <t>maa://41362</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="6" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>雪绒</t>
         </is>
       </c>
       <c r="B289" s="6" t="inlineStr">
         <is>
-          <t>CB-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="C289" s="7" t="inlineStr">
@@ -13866,19 +13965,19 @@
       </c>
       <c r="D289" s="19" t="inlineStr">
         <is>
-          <t>maa://29635</t>
+          <t>maa://20978</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="6" t="inlineStr">
         <is>
-          <t>斥罪</t>
+          <t>子月</t>
         </is>
       </c>
       <c r="B290" s="6" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C290" s="7" t="inlineStr">
@@ -13888,63 +13987,63 @@
       </c>
       <c r="D290" s="19" t="inlineStr">
         <is>
-          <t>maa://38296</t>
+          <t>maa://21002</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="6" t="inlineStr">
         <is>
-          <t>缄默德克萨斯</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B291" s="6" t="inlineStr">
         <is>
-          <t>CB-8</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C291" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D291" s="19" t="inlineStr">
         <is>
-          <t>maa://20899, maa://46332</t>
+          <t>maa://39165</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="6" t="inlineStr">
         <is>
-          <t>谜图</t>
+          <t>伺夜</t>
         </is>
       </c>
       <c r="B292" s="6" t="inlineStr">
         <is>
-          <t>9-4</t>
+          <t>IS-6</t>
         </is>
       </c>
       <c r="C292" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D292" s="19" t="inlineStr">
         <is>
-          <t>maa://53353</t>
+          <t>maa://48267, maa://48266</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="6" t="inlineStr">
         <is>
-          <t>和弦</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B293" s="6" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>CB-4</t>
         </is>
       </c>
       <c r="C293" s="7" t="inlineStr">
@@ -13954,63 +14053,63 @@
       </c>
       <c r="D293" s="19" t="inlineStr">
         <is>
-          <t>maa://20881</t>
+          <t>maa://29635</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="6" t="inlineStr">
         <is>
-          <t>焰影苇草</t>
+          <t>斥罪</t>
         </is>
       </c>
       <c r="B294" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>IS-7</t>
         </is>
       </c>
       <c r="C294" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D294" s="19" t="inlineStr">
         <is>
-          <t>maa://30710, maa://36845, maa://31558, *maa://30668</t>
+          <t>maa://38296</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="6" t="inlineStr">
         <is>
-          <t>截云</t>
+          <t>缄默德克萨斯</t>
         </is>
       </c>
       <c r="B295" s="6" t="inlineStr">
         <is>
-          <t>S2-2</t>
+          <t>CB-8</t>
         </is>
       </c>
       <c r="C295" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D295" s="19" t="inlineStr">
         <is>
-          <t>maa://20902</t>
+          <t>maa://20899, maa://46332</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="6" t="inlineStr">
         <is>
-          <t>火哨</t>
+          <t>谜图</t>
         </is>
       </c>
       <c r="B296" s="6" t="inlineStr">
         <is>
-          <t>S4-6</t>
+          <t>9-4</t>
         </is>
       </c>
       <c r="C296" s="7" t="inlineStr">
@@ -14020,173 +14119,173 @@
       </c>
       <c r="D296" s="19" t="inlineStr">
         <is>
-          <t>maa://29159</t>
+          <t>maa://53353</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="6" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>和弦</t>
         </is>
       </c>
       <c r="B297" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C297" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D297" s="19" t="inlineStr">
         <is>
-          <t>maa://25774, maa://28133, maa://22469</t>
+          <t>maa://20881</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="6" t="inlineStr">
         <is>
-          <t>林</t>
+          <t>焰影苇草</t>
         </is>
       </c>
       <c r="B298" s="6" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C298" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D298" s="19" t="inlineStr">
         <is>
-          <t>maa://47882</t>
+          <t>maa://30710, maa://36845, maa://31558, *maa://30668</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="6" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>截云</t>
         </is>
       </c>
       <c r="B299" s="6" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>S2-2</t>
         </is>
       </c>
       <c r="C299" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D299" s="19" t="inlineStr">
         <is>
-          <t>maa://32414, maa://39155, *maa://32505</t>
+          <t>maa://20902</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="6" t="inlineStr">
         <is>
-          <t>重岳</t>
+          <t>火哨</t>
         </is>
       </c>
       <c r="B300" s="6" t="inlineStr">
         <is>
-          <t>GA-5</t>
+          <t>S4-6</t>
         </is>
       </c>
       <c r="C300" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D300" s="19" t="inlineStr">
         <is>
-          <t>maa://45799, maa://57199</t>
+          <t>maa://29159</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="6" t="inlineStr">
         <is>
-          <t>铎铃</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B301" s="6" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C301" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D301" s="19" t="inlineStr">
         <is>
-          <t>maa://42312</t>
+          <t>maa://25774, maa://28133, maa://22469</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="6" t="inlineStr">
         <is>
-          <t>仇白</t>
+          <t>林</t>
         </is>
       </c>
       <c r="B302" s="6" t="inlineStr">
         <is>
-          <t>WB-7</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="C302" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D302" s="19" t="inlineStr">
         <is>
-          <t>maa://36642, maa://36867, maa://39155</t>
+          <t>maa://47882</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="6" t="inlineStr">
         <is>
-          <t>火龙S黑角</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B303" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C303" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D303" s="19" t="inlineStr">
         <is>
-          <t>maa://39167</t>
+          <t>maa://32414, maa://39155, *maa://32505</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="6" t="inlineStr">
         <is>
-          <t>麒麟R夜刀</t>
+          <t>重岳</t>
         </is>
       </c>
       <c r="B304" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>GA-5</t>
         </is>
       </c>
       <c r="C304" s="7" t="inlineStr">
@@ -14196,19 +14295,19 @@
       </c>
       <c r="D304" s="19" t="inlineStr">
         <is>
-          <t>maa://29005, *maa://31560</t>
+          <t>maa://45799, maa://57199</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="6" t="inlineStr">
         <is>
-          <t>休谟斯</t>
+          <t>铎铃</t>
         </is>
       </c>
       <c r="B305" s="6" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="C305" s="7" t="inlineStr">
@@ -14218,41 +14317,41 @@
       </c>
       <c r="D305" s="19" t="inlineStr">
         <is>
-          <t>maa://39168</t>
+          <t>maa://42312</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="6" t="inlineStr">
         <is>
-          <t>摩根</t>
+          <t>仇白</t>
         </is>
       </c>
       <c r="B306" s="6" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>WB-7</t>
         </is>
       </c>
       <c r="C306" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D306" s="19" t="inlineStr">
         <is>
-          <t>maa://39169</t>
+          <t>maa://36642, maa://36867, maa://39155</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="6" t="inlineStr">
         <is>
-          <t>洋灰</t>
+          <t>火龙S黑角</t>
         </is>
       </c>
       <c r="B307" s="6" t="inlineStr">
         <is>
-          <t>IW-EX-6</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C307" s="7" t="inlineStr">
@@ -14262,41 +14361,41 @@
       </c>
       <c r="D307" s="19" t="inlineStr">
         <is>
-          <t>maa://39170</t>
+          <t>maa://39167</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="6" t="inlineStr">
         <is>
-          <t>伊内丝</t>
+          <t>麒麟R夜刀</t>
         </is>
       </c>
       <c r="B308" s="6" t="inlineStr">
         <is>
-          <t>12-12</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C308" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D308" s="19" t="inlineStr">
         <is>
-          <t>maa://50280, maa://49642, maa://49660, maa://70004, *maa://50517</t>
+          <t>maa://29005, *maa://31560</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="6" t="inlineStr">
         <is>
-          <t>玫拉</t>
+          <t>休谟斯</t>
         </is>
       </c>
       <c r="B309" s="6" t="inlineStr">
         <is>
-          <t>S3-5</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C309" s="7" t="inlineStr">
@@ -14306,19 +14405,19 @@
       </c>
       <c r="D309" s="19" t="inlineStr">
         <is>
-          <t>maa://39171</t>
+          <t>maa://39168</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="6" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>摩根</t>
         </is>
       </c>
       <c r="B310" s="6" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="C310" s="7" t="inlineStr">
@@ -14328,19 +14427,19 @@
       </c>
       <c r="D310" s="19" t="inlineStr">
         <is>
-          <t>maa://27939</t>
+          <t>maa://39169</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="6" t="inlineStr">
         <is>
-          <t>淬羽赫默</t>
+          <t>洋灰</t>
         </is>
       </c>
       <c r="B311" s="6" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>IW-EX-6</t>
         </is>
       </c>
       <c r="C311" s="7" t="inlineStr">
@@ -14350,41 +14449,41 @@
       </c>
       <c r="D311" s="19" t="inlineStr">
         <is>
-          <t>maa://53352</t>
+          <t>maa://39170</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="6" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>伊内丝</t>
         </is>
       </c>
       <c r="B312" s="6" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>12-12</t>
         </is>
       </c>
       <c r="C312" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D312" s="19" t="inlineStr">
         <is>
-          <t>maa://29129</t>
+          <t>maa://50280, maa://49642, maa://49660, maa://70004, *maa://50517</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="6" t="inlineStr">
         <is>
-          <t>霍尔海雅</t>
+          <t>玫拉</t>
         </is>
       </c>
       <c r="B313" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>S3-5</t>
         </is>
       </c>
       <c r="C313" s="7" t="inlineStr">
@@ -14394,19 +14493,19 @@
       </c>
       <c r="D313" s="19" t="inlineStr">
         <is>
-          <t>maa://36005</t>
+          <t>maa://39171</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="6" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B314" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C314" s="7" t="inlineStr">
@@ -14416,19 +14515,19 @@
       </c>
       <c r="D314" s="19" t="inlineStr">
         <is>
-          <t>maa://35859</t>
+          <t>maa://27939</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="6" t="inlineStr">
         <is>
-          <t>缪尔赛思</t>
+          <t>淬羽赫默</t>
         </is>
       </c>
       <c r="B315" s="6" t="inlineStr">
         <is>
-          <t>6-12</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C315" s="7" t="inlineStr">
@@ -14438,19 +14537,19 @@
       </c>
       <c r="D315" s="19" t="inlineStr">
         <is>
-          <t>maa://53348</t>
+          <t>maa://53352</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="6" t="inlineStr">
         <is>
-          <t>隐现</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B316" s="6" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C316" s="7" t="inlineStr">
@@ -14460,19 +14559,19 @@
       </c>
       <c r="D316" s="19" t="inlineStr">
         <is>
-          <t>maa://39172</t>
+          <t>maa://29129</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="6" t="inlineStr">
         <is>
-          <t>空构</t>
+          <t>霍尔海雅</t>
         </is>
       </c>
       <c r="B317" s="6" t="inlineStr">
         <is>
-          <t>DM-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C317" s="7" t="inlineStr">
@@ -14482,63 +14581,63 @@
       </c>
       <c r="D317" s="19" t="inlineStr">
         <is>
-          <t>maa://39173</t>
+          <t>maa://36005</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="6" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B318" s="6" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C318" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D318" s="19" t="inlineStr">
         <is>
-          <t>maa://25775, *maa://25393</t>
+          <t>maa://35859</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="6" t="inlineStr">
         <is>
-          <t>圣约送葬人</t>
+          <t>缪尔赛思</t>
         </is>
       </c>
       <c r="B319" s="6" t="inlineStr">
         <is>
-          <t>GA-3</t>
+          <t>6-12</t>
         </is>
       </c>
       <c r="C319" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D319" s="19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://53348</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="6" t="inlineStr">
         <is>
-          <t>寒檀</t>
+          <t>隐现</t>
         </is>
       </c>
       <c r="B320" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C320" s="7" t="inlineStr">
@@ -14548,19 +14647,19 @@
       </c>
       <c r="D320" s="19" t="inlineStr">
         <is>
-          <t>maa://40161</t>
+          <t>maa://39172</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="6" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>空构</t>
         </is>
       </c>
       <c r="B321" s="6" t="inlineStr">
         <is>
-          <t>S2-1</t>
+          <t>DM-2</t>
         </is>
       </c>
       <c r="C321" s="7" t="inlineStr">
@@ -14570,19 +14669,19 @@
       </c>
       <c r="D321" s="19" t="inlineStr">
         <is>
-          <t>maa://25367</t>
+          <t>maa://39173</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="6" t="inlineStr">
         <is>
-          <t>提丰</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B322" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C322" s="7" t="inlineStr">
@@ -14592,41 +14691,41 @@
       </c>
       <c r="D322" s="19" t="inlineStr">
         <is>
-          <t>maa://62755, maa://62761</t>
+          <t>maa://25775, *maa://25393</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="6" t="inlineStr">
         <is>
-          <t>凛视</t>
+          <t>圣约送葬人</t>
         </is>
       </c>
       <c r="B323" s="6" t="inlineStr">
         <is>
-          <t>7-13</t>
+          <t>GA-3</t>
         </is>
       </c>
       <c r="C323" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D323" s="19" t="inlineStr">
         <is>
-          <t>maa://43090</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="6" t="inlineStr">
         <is>
-          <t>苍苔</t>
+          <t>寒檀</t>
         </is>
       </c>
       <c r="B324" s="6" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C324" s="7" t="inlineStr">
@@ -14636,19 +14735,19 @@
       </c>
       <c r="D324" s="19" t="inlineStr">
         <is>
-          <t>maa://28070</t>
+          <t>maa://40161</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="6" t="inlineStr">
         <is>
-          <t>青枳</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B325" s="6" t="inlineStr">
         <is>
-          <t>OF-5</t>
+          <t>S2-1</t>
         </is>
       </c>
       <c r="C325" s="7" t="inlineStr">
@@ -14658,19 +14757,19 @@
       </c>
       <c r="D325" s="19" t="inlineStr">
         <is>
-          <t>maa://28241</t>
+          <t>maa://25367</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="6" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>提丰</t>
         </is>
       </c>
       <c r="B326" s="6" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C326" s="7" t="inlineStr">
@@ -14680,19 +14779,19 @@
       </c>
       <c r="D326" s="19" t="inlineStr">
         <is>
-          <t>maa://25773, *maa://26088</t>
+          <t>maa://62755, maa://62761</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="6" t="inlineStr">
         <is>
-          <t>琳琅诗怀雅</t>
+          <t>凛视</t>
         </is>
       </c>
       <c r="B327" s="6" t="inlineStr">
         <is>
-          <t>11-16</t>
+          <t>7-13</t>
         </is>
       </c>
       <c r="C327" s="7" t="inlineStr">
@@ -14702,41 +14801,41 @@
       </c>
       <c r="D327" s="19" t="inlineStr">
         <is>
-          <t>maa://39239</t>
+          <t>maa://43090</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="6" t="inlineStr">
         <is>
-          <t>纯烬艾雅法拉</t>
+          <t>苍苔</t>
         </is>
       </c>
       <c r="B328" s="6" t="inlineStr">
         <is>
-          <t>FC-5</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C328" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D328" s="19" t="inlineStr">
         <is>
-          <t>maa://39692, *maa://39810</t>
+          <t>maa://28070</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="6" t="inlineStr">
         <is>
-          <t>冰酿</t>
+          <t>青枳</t>
         </is>
       </c>
       <c r="B329" s="6" t="inlineStr">
         <is>
-          <t>S3-3</t>
+          <t>OF-5</t>
         </is>
       </c>
       <c r="C329" s="7" t="inlineStr">
@@ -14746,85 +14845,85 @@
       </c>
       <c r="D329" s="19" t="inlineStr">
         <is>
-          <t>maa://39174</t>
+          <t>maa://28241</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="6" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B330" s="6" t="inlineStr">
         <is>
-          <t>BI-2</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="C330" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D330" s="19" t="inlineStr">
         <is>
-          <t>maa://39175</t>
+          <t>maa://25773, *maa://26088</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="7" t="inlineStr">
         <is>
-          <t>涤火杰西卡</t>
+          <t>琳琅诗怀雅</t>
         </is>
       </c>
       <c r="B331" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>11-16</t>
         </is>
       </c>
       <c r="C331" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D331" s="8" t="inlineStr">
         <is>
-          <t>maa://34715, maa://34867</t>
+          <t>maa://39239</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="7" t="inlineStr">
         <is>
-          <t>维荻</t>
+          <t>纯烬艾雅法拉</t>
         </is>
       </c>
       <c r="B332" s="6" t="inlineStr">
         <is>
-          <t>9-3</t>
+          <t>FC-5</t>
         </is>
       </c>
       <c r="C332" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>maa://39176</t>
+          <t>maa://39692, *maa://39810</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="7" t="inlineStr">
         <is>
-          <t>戴菲恩</t>
+          <t>冰酿</t>
         </is>
       </c>
       <c r="B333" s="6" t="inlineStr">
         <is>
-          <t>WD-6</t>
+          <t>S3-3</t>
         </is>
       </c>
       <c r="C333" s="7" t="inlineStr">
@@ -14834,19 +14933,19 @@
       </c>
       <c r="D333" s="8" t="inlineStr">
         <is>
-          <t>maa://42316</t>
+          <t>maa://39174</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="7" t="inlineStr">
         <is>
-          <t>刺玫</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="B334" s="6" t="inlineStr">
         <is>
-          <t>IC-2</t>
+          <t>BI-2</t>
         </is>
       </c>
       <c r="C334" s="7" t="inlineStr">
@@ -14856,63 +14955,63 @@
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>maa://30680</t>
+          <t>maa://39175</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="7" t="inlineStr">
         <is>
-          <t>赫德雷</t>
+          <t>涤火杰西卡</t>
         </is>
       </c>
       <c r="B335" s="6" t="inlineStr">
         <is>
-          <t>IW-7</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C335" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D335" s="8" t="inlineStr">
         <is>
-          <t>maa://40956</t>
+          <t>maa://34715, maa://34867</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="7" t="inlineStr">
         <is>
-          <t>跃跃</t>
+          <t>维荻</t>
         </is>
       </c>
       <c r="B336" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>9-3</t>
         </is>
       </c>
       <c r="C336" s="7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://39176</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="7" t="inlineStr">
         <is>
-          <t>折光</t>
+          <t>戴菲恩</t>
         </is>
       </c>
       <c r="B337" s="6" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>WD-6</t>
         </is>
       </c>
       <c r="C337" s="7" t="inlineStr">
@@ -14922,19 +15021,19 @@
       </c>
       <c r="D337" s="8" t="inlineStr">
         <is>
-          <t>maa://67818</t>
+          <t>maa://42316</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="7" t="inlineStr">
         <is>
-          <t>深律</t>
+          <t>刺玫</t>
         </is>
       </c>
       <c r="B338" s="6" t="inlineStr">
         <is>
-          <t>LE-4</t>
+          <t>IC-2</t>
         </is>
       </c>
       <c r="C338" s="7" t="inlineStr">
@@ -14944,63 +15043,63 @@
       </c>
       <c r="D338" s="5" t="inlineStr">
         <is>
-          <t>maa://59688</t>
+          <t>maa://30680</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="7" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>赫德雷</t>
         </is>
       </c>
       <c r="B339" s="6" t="inlineStr">
         <is>
-          <t>7-11</t>
+          <t>IW-7</t>
         </is>
       </c>
       <c r="C339" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>maa://34205, *maa://39541</t>
+          <t>maa://40956</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="inlineStr">
         <is>
-          <t>止颂</t>
+          <t>跃跃</t>
         </is>
       </c>
       <c r="B340" s="6" t="inlineStr">
         <is>
-          <t>TW-5</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C340" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D340" s="5" t="inlineStr">
         <is>
-          <t>maa://43092, maa://43093</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="inlineStr">
         <is>
-          <t>薇薇安娜</t>
+          <t>折光</t>
         </is>
       </c>
       <c r="B341" s="6" t="inlineStr">
         <is>
-          <t>MN-3</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C341" s="7" t="inlineStr">
@@ -15010,85 +15109,85 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>maa://44234</t>
+          <t>maa://67818</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="7" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>深律</t>
         </is>
       </c>
       <c r="B342" s="6" t="inlineStr">
         <is>
-          <t>GA-7</t>
+          <t>LE-4</t>
         </is>
       </c>
       <c r="C342" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D342" s="5" t="inlineStr">
         <is>
-          <t>maa://42968, maa://49245</t>
+          <t>maa://59688</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="inlineStr">
         <is>
-          <t>塑心</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B343" s="6" t="inlineStr">
         <is>
-          <t>ZT-8</t>
+          <t>7-11</t>
         </is>
       </c>
       <c r="C343" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>maa://67275</t>
+          <t>maa://34205, *maa://39541</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="7" t="inlineStr">
         <is>
-          <t>哈洛德</t>
+          <t>止颂</t>
         </is>
       </c>
       <c r="B344" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>TW-5</t>
         </is>
       </c>
       <c r="C344" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D344" s="5" t="inlineStr">
         <is>
-          <t>maa://40162</t>
+          <t>maa://43092, maa://43093</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="7" t="inlineStr">
         <is>
-          <t>烈夏</t>
+          <t>薇薇安娜</t>
         </is>
       </c>
       <c r="B345" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>MN-3</t>
         </is>
       </c>
       <c r="C345" s="7" t="inlineStr">
@@ -15098,41 +15197,41 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>maa://37692</t>
+          <t>maa://44234</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="7" t="inlineStr">
         <is>
-          <t>锏</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B346" s="6" t="inlineStr">
         <is>
-          <t>BI-6</t>
+          <t>GA-7</t>
         </is>
       </c>
       <c r="C346" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D346" s="5" t="inlineStr">
         <is>
-          <t>*maa://30671, maa://30669, *maa://37275, *maa://41605</t>
+          <t>maa://42968, maa://49245</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="7" t="inlineStr">
         <is>
-          <t>温米</t>
+          <t>塑心</t>
         </is>
       </c>
       <c r="B347" s="6" t="inlineStr">
         <is>
-          <t>6-11</t>
+          <t>ZT-8</t>
         </is>
       </c>
       <c r="C347" s="7" t="inlineStr">
@@ -15142,41 +15241,41 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>maa://67817</t>
+          <t>maa://67275</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="inlineStr">
         <is>
-          <t>莱伊</t>
+          <t>哈洛德</t>
         </is>
       </c>
       <c r="B348" s="6" t="inlineStr">
         <is>
-          <t>S9-1</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C348" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D348" s="5" t="inlineStr">
         <is>
-          <t>maa://38295, *maa://49332</t>
+          <t>maa://40162</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="inlineStr">
         <is>
-          <t>万顷</t>
+          <t>烈夏</t>
         </is>
       </c>
       <c r="B349" s="6" t="inlineStr">
         <is>
-          <t>9-13</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C349" s="7" t="inlineStr">
@@ -15186,41 +15285,41 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>maa://32417</t>
+          <t>maa://37692</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="inlineStr">
         <is>
-          <t>小满</t>
+          <t>锏</t>
         </is>
       </c>
       <c r="B350" s="6" t="inlineStr">
         <is>
-          <t>9-11</t>
+          <t>BI-6</t>
         </is>
       </c>
       <c r="C350" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D350" s="5" t="inlineStr">
         <is>
-          <t>maa://32419</t>
+          <t>*maa://30671, maa://30669, *maa://37275, *maa://41605</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>温米</t>
         </is>
       </c>
       <c r="B351" s="6" t="inlineStr">
         <is>
-          <t>WB-5</t>
+          <t>6-11</t>
         </is>
       </c>
       <c r="C351" s="7" t="inlineStr">
@@ -15230,63 +15329,63 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>maa://32416</t>
+          <t>maa://67817</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="inlineStr">
         <is>
-          <t>左乐</t>
+          <t>莱伊</t>
         </is>
       </c>
       <c r="B352" s="6" t="inlineStr">
         <is>
-          <t>RI-7</t>
+          <t>S9-1</t>
         </is>
       </c>
       <c r="C352" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D352" s="5" t="inlineStr">
         <is>
-          <t>maa://45800</t>
+          <t>maa://38295, *maa://49332</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="inlineStr">
         <is>
-          <t>黍</t>
+          <t>万顷</t>
         </is>
       </c>
       <c r="B353" s="6" t="inlineStr">
         <is>
-          <t>11-11</t>
+          <t>9-13</t>
         </is>
       </c>
       <c r="C353" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>maa://32647, maa://32415, maa://34677, maa://32892, *maa://32653, *maa://61839, *maa://61275</t>
+          <t>maa://32417</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="inlineStr">
         <is>
-          <t>红隼</t>
+          <t>小满</t>
         </is>
       </c>
       <c r="B354" s="6" t="inlineStr">
         <is>
-          <t>11-18</t>
+          <t>9-11</t>
         </is>
       </c>
       <c r="C354" s="7" t="inlineStr">
@@ -15296,19 +15395,19 @@
       </c>
       <c r="D354" s="5" t="inlineStr">
         <is>
-          <t>maa://32420</t>
+          <t>maa://32419</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="inlineStr">
         <is>
-          <t>导火索</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B355" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>WB-5</t>
         </is>
       </c>
       <c r="C355" s="7" t="inlineStr">
@@ -15318,19 +15417,19 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>maa://35606</t>
+          <t>maa://32416</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="inlineStr">
         <is>
-          <t>双月</t>
+          <t>左乐</t>
         </is>
       </c>
       <c r="B356" s="6" t="inlineStr">
         <is>
-          <t>3-7</t>
+          <t>RI-7</t>
         </is>
       </c>
       <c r="C356" s="7" t="inlineStr">
@@ -15340,58 +15439,58 @@
       </c>
       <c r="D356" s="5" t="inlineStr">
         <is>
-          <t>maa://34716</t>
+          <t>maa://45800</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="inlineStr">
         <is>
-          <t>医生</t>
+          <t>黍</t>
         </is>
       </c>
       <c r="B357" s="6" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>11-11</t>
         </is>
       </c>
       <c r="C357" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>maa://39179</t>
+          <t>maa://32647, maa://32415, maa://34677, maa://32892, *maa://32653, *maa://61839, *maa://61275</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="inlineStr">
         <is>
-          <t>艾拉</t>
+          <t>红隼</t>
         </is>
       </c>
       <c r="B358" s="6" t="inlineStr">
         <is>
-          <t>DM-EX-1</t>
+          <t>11-18</t>
         </is>
       </c>
       <c r="C358" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D358" s="5" t="inlineStr">
         <is>
-          <t>maa://34865, maa://34717</t>
+          <t>maa://32420</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="inlineStr">
         <is>
-          <t>露托</t>
+          <t>导火索</t>
         </is>
       </c>
       <c r="B359" s="6" t="inlineStr">
@@ -15406,41 +15505,41 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>maa://39180</t>
+          <t>maa://35606</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="inlineStr">
         <is>
-          <t>奥达</t>
+          <t>双月</t>
         </is>
       </c>
       <c r="B360" s="6" t="inlineStr">
         <is>
-          <t>S3-6</t>
+          <t>3-7</t>
         </is>
       </c>
       <c r="C360" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D360" s="5" t="inlineStr">
         <is>
-          <t>maa://45834, *maa://45833</t>
+          <t>maa://34716</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="inlineStr">
         <is>
-          <t>阿罗玛</t>
+          <t>医生</t>
         </is>
       </c>
       <c r="B361" s="6" t="inlineStr">
         <is>
-          <t>GT-HX-3</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="C361" s="7" t="inlineStr">
@@ -15450,305 +15549,305 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>maa://39181</t>
+          <t>maa://39179</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>艾拉</t>
         </is>
       </c>
       <c r="B362" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>DM-EX-1</t>
         </is>
       </c>
       <c r="C362" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D362" s="5" t="inlineStr">
         <is>
-          <t>maa://36868, maa://35996, maa://47349, **maa://71203</t>
+          <t>maa://34865, maa://34717</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="inlineStr">
         <is>
-          <t>阿斯卡纶</t>
+          <t>露托</t>
         </is>
       </c>
       <c r="B363" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C363" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>maa://49696, maa://49695, maa://49758, *maa://52357</t>
+          <t>maa://39180</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="inlineStr">
         <is>
-          <t>历阵锐枪芬</t>
+          <t>奥达</t>
         </is>
       </c>
       <c r="B364" s="6" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>S3-6</t>
         </is>
       </c>
       <c r="C364" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D364" s="5" t="inlineStr">
         <is>
-          <t>maa://36647</t>
+          <t>maa://45834, *maa://45833</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="inlineStr">
         <is>
-          <t>魔王</t>
+          <t>阿罗玛</t>
         </is>
       </c>
       <c r="B365" s="6" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>GT-HX-3</t>
         </is>
       </c>
       <c r="C365" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>maa://42299, *maa://42224</t>
+          <t>maa://39181</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B366" s="6" t="inlineStr">
         <is>
-          <t>14-9</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C366" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D366" s="5" t="inlineStr">
         <is>
-          <t>maa://49648, *maa://49662</t>
+          <t>maa://36868, maa://35996, maa://47349, **maa://71203</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="inlineStr">
         <is>
-          <t>逻各斯</t>
+          <t>阿斯卡纶</t>
         </is>
       </c>
       <c r="B367" s="6" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C367" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>maa://36646, maa://36845, maa://51007, *maa://70752, *maa://71932</t>
+          <t>maa://49696, maa://49695, maa://49758, *maa://52357</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="inlineStr">
         <is>
-          <t>维什戴尔</t>
+          <t>历阵锐枪芬</t>
         </is>
       </c>
       <c r="B368" s="6" t="inlineStr">
         <is>
-          <t>DM-5</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="C368" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D368" s="5" t="inlineStr">
         <is>
-          <t>maa://36645, maa://36841, maa://37484, maa://37858</t>
+          <t>maa://36647</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="inlineStr">
         <is>
-          <t>阿米娅</t>
+          <t>魔王</t>
         </is>
       </c>
       <c r="B369" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C369" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>maa://42635, *maa://50629, *maa://48859</t>
+          <t>maa://42299, *maa://42224</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="inlineStr">
         <is>
-          <t>深巡</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B370" s="6" t="inlineStr">
         <is>
-          <t>SN-5</t>
+          <t>14-9</t>
         </is>
       </c>
       <c r="C370" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D370" s="5" t="inlineStr">
         <is>
-          <t>maa://39183</t>
+          <t>maa://49648, *maa://49662</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="inlineStr">
         <is>
-          <t>海霓</t>
+          <t>逻各斯</t>
         </is>
       </c>
       <c r="B371" s="6" t="inlineStr">
         <is>
-          <t>SV-4</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="C371" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>maa://39184</t>
+          <t>maa://36646, maa://36845, maa://51007, *maa://70752, *maa://71932</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="inlineStr">
         <is>
-          <t>乌尔比安</t>
+          <t>维什戴尔</t>
         </is>
       </c>
       <c r="B372" s="6" t="inlineStr">
         <is>
-          <t>SV-6</t>
+          <t>DM-5</t>
         </is>
       </c>
       <c r="C372" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D372" s="5" t="inlineStr">
         <is>
-          <t>maa://40957, maa://48026, maa://44635, maa://41035, *maa://60251, maa://44660, *maa://41128</t>
+          <t>maa://36645, maa://36841, maa://37484, maa://37858</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="inlineStr">
         <is>
-          <t>渡桥</t>
+          <t>阿米娅</t>
         </is>
       </c>
       <c r="B373" s="6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C373" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>maa://40164</t>
+          <t>maa://42635, *maa://50629, *maa://48859</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="inlineStr">
         <is>
-          <t>妮芙</t>
+          <t>深巡</t>
         </is>
       </c>
       <c r="B374" s="6" t="inlineStr">
         <is>
-          <t>14-7</t>
+          <t>SN-5</t>
         </is>
       </c>
       <c r="C374" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D374" s="5" t="inlineStr">
         <is>
-          <t>maa://63883, maa://64045, **maa://64041</t>
+          <t>maa://39183</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="inlineStr">
         <is>
-          <t>锡人</t>
+          <t>海霓</t>
         </is>
       </c>
       <c r="B375" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>SV-4</t>
         </is>
       </c>
       <c r="C375" s="7" t="inlineStr">
@@ -15758,85 +15857,85 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>maa://48268</t>
+          <t>maa://39184</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="inlineStr">
         <is>
-          <t>衡沙</t>
+          <t>乌尔比安</t>
         </is>
       </c>
       <c r="B376" s="6" t="inlineStr">
         <is>
-          <t>DV-2</t>
+          <t>SV-6</t>
         </is>
       </c>
       <c r="C376" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D376" s="5" t="inlineStr">
         <is>
-          <t>maa://40165</t>
+          <t>maa://40957, maa://48026, maa://44635, maa://41035, *maa://60251, maa://44660, *maa://41128</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="inlineStr">
         <is>
-          <t>娜仁图亚</t>
+          <t>渡桥</t>
         </is>
       </c>
       <c r="B377" s="6" t="inlineStr">
         <is>
-          <t>WB-6</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="C377" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>maa://71182, maa://70756, *maa://71524, *maa://72244</t>
+          <t>maa://40164</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="inlineStr">
         <is>
-          <t>佩佩</t>
+          <t>妮芙</t>
         </is>
       </c>
       <c r="B378" s="6" t="inlineStr">
         <is>
-          <t>3-8</t>
+          <t>14-7</t>
         </is>
       </c>
       <c r="C378" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D378" s="5" t="inlineStr">
         <is>
-          <t>maa://45798</t>
+          <t>maa://63883, maa://64045, **maa://64041</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="inlineStr">
         <is>
-          <t>森西</t>
+          <t>锡人</t>
         </is>
       </c>
       <c r="B379" s="6" t="inlineStr">
         <is>
-          <t>1-12</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C379" s="7" t="inlineStr">
@@ -15846,85 +15945,85 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>maa://42331</t>
+          <t>maa://48268</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="inlineStr">
         <is>
-          <t>齐尔查克</t>
+          <t>衡沙</t>
         </is>
       </c>
       <c r="B380" s="6" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>DV-2</t>
         </is>
       </c>
       <c r="C380" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D380" s="5" t="inlineStr">
         <is>
-          <t>maa://42333, *maa://50518, *maa://41977</t>
+          <t>maa://40165</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="inlineStr">
         <is>
-          <t>莱欧斯</t>
+          <t>娜仁图亚</t>
         </is>
       </c>
       <c r="B381" s="6" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>WB-6</t>
         </is>
       </c>
       <c r="C381" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>maa://42338</t>
+          <t>maa://71182, maa://70756, *maa://71524, *maa://72244</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="inlineStr">
         <is>
-          <t>玛露西尔</t>
+          <t>佩佩</t>
         </is>
       </c>
       <c r="B382" s="6" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>3-8</t>
         </is>
       </c>
       <c r="C382" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D382" s="5" t="inlineStr">
         <is>
-          <t>maa://41110, *maa://45605</t>
+          <t>maa://45798</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="inlineStr">
         <is>
-          <t>凯瑟琳</t>
+          <t>森西</t>
         </is>
       </c>
       <c r="B383" s="6" t="inlineStr">
         <is>
-          <t>11-7</t>
+          <t>1-12</t>
         </is>
       </c>
       <c r="C383" s="7" t="inlineStr">
@@ -15934,85 +16033,85 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>maa://42343</t>
+          <t>maa://42331</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="inlineStr">
         <is>
-          <t>波卜</t>
+          <t>齐尔查克</t>
         </is>
       </c>
       <c r="B384" s="6" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="C384" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D384" s="5" t="inlineStr">
         <is>
-          <t>maa://43095</t>
+          <t>maa://42333, *maa://50518, *maa://41977</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="7" t="inlineStr">
         <is>
-          <t>维娜·维多利亚</t>
+          <t>莱欧斯</t>
         </is>
       </c>
       <c r="B385" s="6" t="inlineStr">
         <is>
-          <t>9-5</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="C385" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>maa://44233, maa://45570</t>
+          <t>maa://42338</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="7" t="inlineStr">
         <is>
-          <t>裁度</t>
+          <t>玛露西尔</t>
         </is>
       </c>
       <c r="B386" s="6" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="C386" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D386" s="5" t="inlineStr">
         <is>
-          <t>maa://43097</t>
+          <t>maa://41110, *maa://45605</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="7" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>凯瑟琳</t>
         </is>
       </c>
       <c r="B387" s="6" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>11-7</t>
         </is>
       </c>
       <c r="C387" s="7" t="inlineStr">
@@ -16022,14 +16121,14 @@
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>maa://43872</t>
+          <t>maa://42343</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="7" t="inlineStr">
         <is>
-          <t>弑君者</t>
+          <t>波卜</t>
         </is>
       </c>
       <c r="B388" s="6" t="inlineStr">
@@ -16044,63 +16143,63 @@
       </c>
       <c r="D388" s="5" t="inlineStr">
         <is>
-          <t>maa://53307</t>
+          <t>maa://43095</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="7" t="inlineStr">
         <is>
-          <t>忍冬</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B389" s="6" t="inlineStr">
         <is>
-          <t>S2-3</t>
+          <t>9-5</t>
         </is>
       </c>
       <c r="C389" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>maa://43875</t>
+          <t>maa://44233, maa://45570</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="7" t="inlineStr">
         <is>
-          <t>荒芜拉普兰德</t>
+          <t>维娜·维多利亚</t>
         </is>
       </c>
       <c r="B390" s="6" t="inlineStr">
         <is>
-          <t>IS-8</t>
+          <t>7-18</t>
         </is>
       </c>
       <c r="C390" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D390" s="5" t="inlineStr">
         <is>
-          <t>*maa://42970, maa://44745, *maa://44896</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="7" t="inlineStr">
         <is>
-          <t>瑰盐</t>
+          <t>裁度</t>
         </is>
       </c>
       <c r="B391" s="6" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C391" s="7" t="inlineStr">
@@ -16110,19 +16209,19 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>maa://44389</t>
+          <t>maa://43097</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="7" t="inlineStr">
         <is>
-          <t>特克诺</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B392" s="6" t="inlineStr">
         <is>
-          <t>DH-6</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="C392" s="7" t="inlineStr">
@@ -16132,19 +16231,19 @@
       </c>
       <c r="D392" s="5" t="inlineStr">
         <is>
-          <t>maa://59690</t>
+          <t>maa://43872</t>
         </is>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
       <c r="A393" s="13" t="inlineStr">
         <is>
-          <t>引星棘刺</t>
+          <t>弑君者</t>
         </is>
       </c>
       <c r="B393" s="20" t="inlineStr">
         <is>
-          <t>OF-7</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C393" s="13" t="inlineStr">
@@ -16154,19 +16253,19 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>maa://48113</t>
+          <t>maa://53307</t>
         </is>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
       <c r="A394" s="13" t="inlineStr">
         <is>
-          <t>行箸</t>
+          <t>忍冬</t>
         </is>
       </c>
       <c r="B394" s="20" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>S2-3</t>
         </is>
       </c>
       <c r="C394" s="13" t="inlineStr">
@@ -16176,41 +16275,41 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>maa://45807</t>
+          <t>maa://43875</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="13" t="inlineStr">
         <is>
-          <t>寻澜</t>
+          <t>荒芜拉普兰德</t>
         </is>
       </c>
       <c r="B395" s="13" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>IS-8</t>
         </is>
       </c>
       <c r="C395" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>maa://50552</t>
+          <t>*maa://42970, maa://44745, *maa://44896</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="13" t="inlineStr">
         <is>
-          <t>烛煌</t>
+          <t>瑰盐</t>
         </is>
       </c>
       <c r="B396" s="13" t="inlineStr">
         <is>
-          <t>6-10</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C396" s="13" t="inlineStr">
@@ -16220,41 +16319,41 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>maa://63890</t>
+          <t>maa://44389</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="13" t="inlineStr">
         <is>
-          <t>诺威尔</t>
+          <t>特克诺</t>
         </is>
       </c>
       <c r="B397" s="13" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>DH-6</t>
         </is>
       </c>
       <c r="C397" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>*maa://47175, maa://47174</t>
+          <t>maa://59690</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="13" t="inlineStr">
         <is>
-          <t>隐德来希</t>
+          <t>引星棘刺</t>
         </is>
       </c>
       <c r="B398" s="13" t="inlineStr">
         <is>
-          <t>10-12</t>
+          <t>OF-7</t>
         </is>
       </c>
       <c r="C398" s="13" t="inlineStr">
@@ -16264,41 +16363,41 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>maa://47023</t>
+          <t>maa://48113</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="13" t="inlineStr">
         <is>
-          <t>水灯心</t>
+          <t>行箸</t>
         </is>
       </c>
       <c r="B399" s="13" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="C399" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://45807</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="13" t="inlineStr">
         <is>
-          <t>钼铅</t>
+          <t>寻澜</t>
         </is>
       </c>
       <c r="B400" s="13" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="C400" s="13" t="inlineStr">
@@ -16308,63 +16407,63 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>maa://48618</t>
+          <t>maa://50552</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="13" t="inlineStr">
         <is>
-          <t>死芒</t>
+          <t>烛煌</t>
         </is>
       </c>
       <c r="B401" s="13" t="inlineStr">
         <is>
-          <t>4-8</t>
+          <t>6-10</t>
         </is>
       </c>
       <c r="C401" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>maa://59533, maa://59577</t>
+          <t>maa://63890</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="13" t="inlineStr">
         <is>
-          <t>骋风</t>
+          <t>诺威尔</t>
         </is>
       </c>
       <c r="B402" s="13" t="inlineStr">
         <is>
-          <t>SN-2</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="C402" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>maa://51908</t>
+          <t>*maa://47175, maa://47174</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="13" t="inlineStr">
         <is>
-          <t>阿兰娜</t>
+          <t>隐德来希</t>
         </is>
       </c>
       <c r="B403" s="13" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>10-12</t>
         </is>
       </c>
       <c r="C403" s="13" t="inlineStr">
@@ -16374,85 +16473,85 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>maa://59691</t>
+          <t>maa://47023</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="13" t="inlineStr">
         <is>
-          <t>信仰搅拌机</t>
+          <t>水灯心</t>
         </is>
       </c>
       <c r="B404" s="13" t="inlineStr">
         <is>
-          <t>14-5</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="C404" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>maa://51898, maa://57241</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="13" t="inlineStr">
         <is>
-          <t>蕾缪安</t>
+          <t>钼铅</t>
         </is>
       </c>
       <c r="B405" s="13" t="inlineStr">
         <is>
-          <t>13-13</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C405" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>maa://51880, maa://56651, maa://51878</t>
+          <t>maa://48618</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="13" t="inlineStr">
         <is>
-          <t>新约能天使</t>
+          <t>死芒</t>
         </is>
       </c>
       <c r="B406" s="13" t="inlineStr">
         <is>
-          <t>GA-EX-5</t>
+          <t>4-8</t>
         </is>
       </c>
       <c r="C406" s="13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>maa://51872, maa://51876, *maa://63228, maa://51873, *maa://62047</t>
+          <t>maa://59533, maa://59577</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="13" t="inlineStr">
         <is>
-          <t>Miss.Christine</t>
+          <t>骋风</t>
         </is>
       </c>
       <c r="B407" s="13" t="inlineStr">
         <is>
-          <t>DM-7</t>
+          <t>SN-2</t>
         </is>
       </c>
       <c r="C407" s="13" t="inlineStr">
@@ -16462,195 +16561,195 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>maa://67814</t>
+          <t>maa://51908</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="13" t="inlineStr">
         <is>
-          <t>酒神</t>
+          <t>阿兰娜</t>
         </is>
       </c>
       <c r="B408" s="13" t="inlineStr">
         <is>
-          <t>9-6</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C408" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>maa://60449, maa://59493</t>
+          <t>maa://59691</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="13" t="inlineStr">
         <is>
-          <t>录武官</t>
+          <t>信仰搅拌机</t>
         </is>
       </c>
       <c r="B409" s="13" t="inlineStr">
         <is>
-          <t>HS-5</t>
+          <t>14-5</t>
         </is>
       </c>
       <c r="C409" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>maa://67815</t>
+          <t>maa://51898, maa://57241</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="13" t="inlineStr">
         <is>
-          <t>司霆惊蛰</t>
+          <t>蕾缪安</t>
         </is>
       </c>
       <c r="B410" s="13" t="inlineStr">
         <is>
-          <t>DV-7</t>
+          <t>13-13</t>
         </is>
       </c>
       <c r="C410" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>maa://62756</t>
+          <t>maa://51880, maa://56651, maa://51878</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="13" t="inlineStr">
         <is>
-          <t>吉星</t>
+          <t>新约能天使</t>
         </is>
       </c>
       <c r="B411" s="13" t="inlineStr">
         <is>
-          <t>S5-9</t>
+          <t>GA-EX-5</t>
         </is>
       </c>
       <c r="C411" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>maa://67816</t>
+          <t>maa://51872, maa://51876, *maa://63228, maa://51873, *maa://62047</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="13" t="inlineStr">
         <is>
-          <t>遥</t>
+          <t>Miss.Christine</t>
         </is>
       </c>
       <c r="B412" s="13" t="inlineStr">
         <is>
-          <t>7-14</t>
+          <t>DM-7</t>
         </is>
       </c>
       <c r="C412" s="13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>maa://52505, maa://64040, *maa://66377</t>
+          <t>maa://67814</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="13" t="inlineStr">
         <is>
-          <t>祐天寺若麦</t>
+          <t>酒神</t>
         </is>
       </c>
       <c r="B413" s="13" t="inlineStr">
         <is>
-          <t>ZT-4</t>
+          <t>9-6</t>
         </is>
       </c>
       <c r="C413" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>maa://67090</t>
+          <t>maa://60449, maa://59493</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="13" t="inlineStr">
         <is>
-          <t>八幡海铃</t>
+          <t>录武官</t>
         </is>
       </c>
       <c r="B414" s="13" t="inlineStr">
         <is>
-          <t>BB-7</t>
+          <t>HS-5</t>
         </is>
       </c>
       <c r="C414" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>maa://67388, *maa://71184</t>
+          <t>maa://67815</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="13" t="inlineStr">
         <is>
-          <t>若叶睦</t>
+          <t>司霆惊蛰</t>
         </is>
       </c>
       <c r="B415" s="13" t="inlineStr">
         <is>
-          <t>13-16</t>
+          <t>DV-7</t>
         </is>
       </c>
       <c r="C415" s="13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>maa://67089, maa://67271</t>
+          <t>maa://62756</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="13" t="inlineStr">
         <is>
-          <t>三角初华</t>
+          <t>吉星</t>
         </is>
       </c>
       <c r="B416" s="13" t="inlineStr">
         <is>
-          <t>ZT-6</t>
+          <t>S5-9</t>
         </is>
       </c>
       <c r="C416" s="13" t="inlineStr">
@@ -16660,41 +16759,41 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>maa://67088</t>
+          <t>maa://67816</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="13" t="inlineStr">
         <is>
-          <t>丰川祥子</t>
+          <t>遥</t>
         </is>
       </c>
       <c r="B417" s="13" t="inlineStr">
         <is>
-          <t>IS-7</t>
+          <t>7-14</t>
         </is>
       </c>
       <c r="C417" s="13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>maa://67087, maa://67268, *maa://67269, *maa://67648</t>
+          <t>maa://52505, maa://64040, *maa://66377</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="13" t="inlineStr">
         <is>
-          <t>冬时</t>
+          <t>斩业星熊</t>
         </is>
       </c>
       <c r="B418" s="13" t="inlineStr">
         <is>
-          <t>R8-2</t>
+          <t>OF-8</t>
         </is>
       </c>
       <c r="C418" s="13" t="inlineStr">
@@ -16711,44 +16810,264 @@
     <row r="419">
       <c r="A419" s="13" t="inlineStr">
         <is>
-          <t>折桠</t>
+          <t>祐天寺若麦</t>
         </is>
       </c>
       <c r="B419" s="13" t="inlineStr">
         <is>
-          <t>MB-5</t>
+          <t>ZT-4</t>
         </is>
       </c>
       <c r="C419" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>maa://67090</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="13" t="inlineStr">
         <is>
+          <t>八幡海铃</t>
+        </is>
+      </c>
+      <c r="B420" s="13" t="inlineStr">
+        <is>
+          <t>BB-7</t>
+        </is>
+      </c>
+      <c r="C420" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>maa://67388, *maa://71184</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="13" t="inlineStr">
+        <is>
+          <t>若叶睦</t>
+        </is>
+      </c>
+      <c r="B421" s="13" t="inlineStr">
+        <is>
+          <t>13-16</t>
+        </is>
+      </c>
+      <c r="C421" s="13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>maa://67089, maa://67271</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="13" t="inlineStr">
+        <is>
+          <t>三角初华</t>
+        </is>
+      </c>
+      <c r="B422" s="13" t="inlineStr">
+        <is>
+          <t>ZT-6</t>
+        </is>
+      </c>
+      <c r="C422" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>maa://67088</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="13" t="inlineStr">
+        <is>
+          <t>丰川祥子</t>
+        </is>
+      </c>
+      <c r="B423" s="13" t="inlineStr">
+        <is>
+          <t>IS-7</t>
+        </is>
+      </c>
+      <c r="C423" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>maa://67087, maa://67268, *maa://67269, *maa://67648</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="13" t="inlineStr">
+        <is>
+          <t>冬时</t>
+        </is>
+      </c>
+      <c r="B424" s="13" t="inlineStr">
+        <is>
+          <t>R8-2</t>
+        </is>
+      </c>
+      <c r="C424" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="13" t="inlineStr">
+        <is>
+          <t>折桠</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="inlineStr">
+        <is>
+          <t>MB-5</t>
+        </is>
+      </c>
+      <c r="C425" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="13" t="inlineStr">
+        <is>
           <t>真言</t>
         </is>
       </c>
-      <c r="B420" s="13" t="inlineStr">
+      <c r="B426" s="13" t="inlineStr">
         <is>
           <t>FC-5</t>
         </is>
       </c>
-      <c r="C420" s="13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr">
+      <c r="C426" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
         <is>
           <t>maa://70877</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="13" t="inlineStr">
+        <is>
+          <t>协律</t>
+        </is>
+      </c>
+      <c r="B427" s="13" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="C427" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="13" t="inlineStr">
+        <is>
+          <t>雪猎</t>
+        </is>
+      </c>
+      <c r="B428" s="13" t="inlineStr">
+        <is>
+          <t>BI-1</t>
+        </is>
+      </c>
+      <c r="C428" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="13" t="inlineStr">
+        <is>
+          <t>溯光星源</t>
+        </is>
+      </c>
+      <c r="B429" s="13" t="inlineStr">
+        <is>
+          <t>BI-6</t>
+        </is>
+      </c>
+      <c r="C429" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="13" t="inlineStr">
+        <is>
+          <t>圣聆初雪</t>
+        </is>
+      </c>
+      <c r="B430" s="13" t="inlineStr">
+        <is>
+          <t>BI-7</t>
+        </is>
+      </c>
+      <c r="C430" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>maa://73227</t>
         </is>
       </c>
     </row>

--- a/Excel/悖论&模组作业用户版.xlsx
+++ b/Excel/悖论&模组作业用户版.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="T4" s="18" t="inlineStr">
         <is>
-          <t>maa://27295, maa://32509, maa://31008, maa://70489, maa://22754</t>
+          <t>maa://27295, maa://32509, maa://70489, maa://31008, maa://22754</t>
         </is>
       </c>
       <c r="U4" s="15" t="n"/>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="AF4" s="18" t="inlineStr">
         <is>
-          <t>maa://39394, maa://30062</t>
+          <t>*maa://39394, maa://30062</t>
         </is>
       </c>
       <c r="AG4" s="12" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P6" s="18" t="inlineStr">
         <is>
-          <t>maa://31836, *maa://30381</t>
+          <t>maa://31836, maa://30381</t>
         </is>
       </c>
       <c r="Q6" s="15" t="n"/>
@@ -1452,7 +1452,7 @@
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>更新日期：2025.11.13 13:22:25</t>
+          <t>更新日期：2025.11.16 13:20:51</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>maa://21476</t>
+          <t>maa://21476, *maa://39431</t>
         </is>
       </c>
       <c r="E8" s="15" t="n"/>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="L15" s="18" t="inlineStr">
         <is>
-          <t>maa://21334, maa://73742</t>
+          <t>*maa://21334, maa://73742</t>
         </is>
       </c>
       <c r="M15" s="15" t="n"/>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AF15" s="18" t="inlineStr">
         <is>
-          <t>maa://36666, maa://21364, *maa://22766, maa://68306</t>
+          <t>maa://36666, maa://21364, maa://68306, *maa://22766</t>
         </is>
       </c>
       <c r="AG15" s="12" t="n"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="AF18" s="18" t="inlineStr">
         <is>
-          <t>maa://47854, **maa://68715, *maa://74015</t>
+          <t>maa://47854, **maa://68715, maa://74015</t>
         </is>
       </c>
       <c r="AG18" s="12" t="n"/>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>maa://25198, maa://36680, maa://21432</t>
+          <t>maa://36680, maa://25198, maa://21432</t>
         </is>
       </c>
       <c r="E20" s="15" t="n"/>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AB21" s="18" t="inlineStr">
         <is>
-          <t>maa://21443, maa://52223</t>
+          <t>maa://52223, maa://21443</t>
         </is>
       </c>
       <c r="AC21" s="15" t="n"/>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="T32" s="18" t="inlineStr">
         <is>
-          <t>maa://42859, *maa://41108, maa://41238, maa://45523</t>
+          <t>maa://42859, maa://41108, maa://41238, maa://45523</t>
         </is>
       </c>
       <c r="U32" s="15" t="n"/>
@@ -5285,7 +5285,7 @@
       </c>
       <c r="P37" s="18" t="inlineStr">
         <is>
-          <t>maa://21280, *maa://21239</t>
+          <t>maa://21280, **maa://21239</t>
         </is>
       </c>
       <c r="Q37" s="15" t="n"/>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="T43" s="18" t="inlineStr">
         <is>
-          <t>maa://43198, *maa://46286</t>
+          <t>maa://43198, maa://46286</t>
         </is>
       </c>
       <c r="U43" s="15" t="n"/>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>maa://29768, maa://56386, maa://27728</t>
+          <t>maa://56386, maa://29768, maa://27728</t>
         </is>
       </c>
       <c r="I44" s="15" t="n"/>
@@ -7269,7 +7269,7 @@
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="17" t="inlineStr">
         <is>
-          <t>更新日期：2025.11.13 13:22:25</t>
+          <t>更新日期：2025.11.16 13:20:51</t>
         </is>
       </c>
       <c r="E1" s="16" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D53" s="19" t="inlineStr">
         <is>
-          <t>maa://20953, maa://31173</t>
+          <t>maa://31173, maa://20953</t>
         </is>
       </c>
     </row>
@@ -9054,12 +9054,12 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D66" s="19" t="inlineStr">
         <is>
-          <t>maa://28567, maa://30525, maa://38735</t>
+          <t>maa://28567, maa://30525, maa://38735, *maa://70681</t>
         </is>
       </c>
     </row>
@@ -11188,12 +11188,12 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D163" s="19" t="inlineStr">
         <is>
-          <t>maa://44232, *maa://45603</t>
+          <t>maa://44232, *maa://45603, *maa://71762</t>
         </is>
       </c>
     </row>
@@ -11347,7 +11347,7 @@
       </c>
       <c r="D170" s="19" t="inlineStr">
         <is>
-          <t>maa://47950, maa://20975, *maa://30806</t>
+          <t>maa://47950, *maa://20975, *maa://30806</t>
         </is>
       </c>
     </row>
@@ -16798,12 +16798,12 @@
       </c>
       <c r="C418" s="13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>maa://73193</t>
+          <t>maa://73193, *maa://74820</t>
         </is>
       </c>
     </row>
@@ -16913,7 +16913,7 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>maa://67087, maa://67268, *maa://67269, maa://67648</t>
+          <t>maa://67087, maa://67268, *maa://67269, *maa://67648</t>
         </is>
       </c>
     </row>
@@ -17067,7 +17067,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>maa://73227, maa://73422, *maa://73447</t>
+          <t>maa://73227, maa://73422, maa://73447</t>
         </is>
       </c>
     </row>
